--- a/research/traditional_assets/database/data/singapore/singapore_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_cable_tv.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07143251743292804</v>
+        <v>0.07134843215329206</v>
       </c>
       <c r="C2">
-        <v>923.2429437874822</v>
+        <v>914.1668000367197</v>
       </c>
       <c r="D2">
-        <v>871.8429437874822</v>
+        <v>872.7618760968072</v>
       </c>
       <c r="E2">
-        <v>-896.3076060087469</v>
+        <v>-886.3125299486594</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.99507606008747</v>
       </c>
       <c r="G2">
         <v>51.4</v>
@@ -1445,28 +1445,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5027523258223997</v>
       </c>
       <c r="N2">
-        <v>99.55999999999999</v>
+        <v>99.05724767417759</v>
       </c>
       <c r="O2">
-        <v>16.9252</v>
+        <v>16.83973210461019</v>
       </c>
       <c r="P2">
-        <v>82.63479999999998</v>
+        <v>82.2175155695674</v>
       </c>
       <c r="Q2">
-        <v>122.3348</v>
+        <v>121.9175155695674</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07143251743292804</v>
+        <v>0.07164741631645663</v>
       </c>
       <c r="T2">
-        <v>0.5919749984509941</v>
+        <v>0.5969380211652802</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>198.0299143064933</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07134843215329206</v>
+        <v>0.07126434687365608</v>
       </c>
       <c r="C3">
-        <v>914.1668000367197</v>
+        <v>905.0925954599336</v>
       </c>
       <c r="D3">
-        <v>872.7618760968072</v>
+        <v>873.6827475801085</v>
       </c>
       <c r="E3">
-        <v>-886.3125299486594</v>
+        <v>-876.317453888572</v>
       </c>
       <c r="F3">
-        <v>9.99507606008747</v>
+        <v>19.99015212017494</v>
       </c>
       <c r="G3">
         <v>51.4</v>
@@ -1527,28 +1527,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M3">
-        <v>0.5027523258223997</v>
+        <v>1.005504651644799</v>
       </c>
       <c r="N3">
-        <v>99.05724767417759</v>
+        <v>98.55449534835519</v>
       </c>
       <c r="O3">
-        <v>16.83973210461019</v>
+        <v>16.75426420922038</v>
       </c>
       <c r="P3">
-        <v>82.2175155695674</v>
+        <v>81.80023113913481</v>
       </c>
       <c r="Q3">
-        <v>121.9175155695674</v>
+        <v>121.5002311391348</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07164741631645663</v>
+        <v>0.07186670089148581</v>
       </c>
       <c r="T3">
-        <v>0.5969380211652802</v>
+        <v>0.602002330057409</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>198.0299143064933</v>
+        <v>99.01495715324663</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07126434687365608</v>
+        <v>0.07118026159402012</v>
       </c>
       <c r="C4">
-        <v>905.0925954599336</v>
+        <v>896.0203362018103</v>
       </c>
       <c r="D4">
-        <v>873.6827475801085</v>
+        <v>874.6055643820728</v>
       </c>
       <c r="E4">
-        <v>-876.317453888572</v>
+        <v>-866.3223778284845</v>
       </c>
       <c r="F4">
-        <v>19.99015212017494</v>
+        <v>29.98522818026241</v>
       </c>
       <c r="G4">
         <v>51.4</v>
@@ -1609,28 +1609,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M4">
-        <v>1.005504651644799</v>
+        <v>1.508256977467199</v>
       </c>
       <c r="N4">
-        <v>98.55449534835519</v>
+        <v>98.05174302253279</v>
       </c>
       <c r="O4">
-        <v>16.75426420922038</v>
+        <v>16.66879631383058</v>
       </c>
       <c r="P4">
-        <v>81.80023113913481</v>
+        <v>81.38294670870221</v>
       </c>
       <c r="Q4">
-        <v>121.5002311391348</v>
+        <v>121.0829467087022</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07186670089148581</v>
+        <v>0.07209050679795888</v>
       </c>
       <c r="T4">
-        <v>0.602002330057409</v>
+        <v>0.6071710576895815</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>99.01495715324663</v>
+        <v>66.00997143549776</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07118026159402012</v>
+        <v>0.07109617631438414</v>
       </c>
       <c r="C5">
-        <v>896.0203362018103</v>
+        <v>886.9500284330256</v>
       </c>
       <c r="D5">
-        <v>874.6055643820728</v>
+        <v>875.5303326733756</v>
       </c>
       <c r="E5">
-        <v>-866.3223778284845</v>
+        <v>-856.3273017683971</v>
       </c>
       <c r="F5">
-        <v>29.98522818026241</v>
+        <v>39.98030424034988</v>
       </c>
       <c r="G5">
         <v>51.4</v>
@@ -1691,28 +1691,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M5">
-        <v>1.508256977467199</v>
+        <v>2.011009303289599</v>
       </c>
       <c r="N5">
-        <v>98.05174302253279</v>
+        <v>97.54899069671039</v>
       </c>
       <c r="O5">
-        <v>16.66879631383058</v>
+        <v>16.58332841844077</v>
       </c>
       <c r="P5">
-        <v>81.38294670870221</v>
+        <v>80.96566227826962</v>
       </c>
       <c r="Q5">
-        <v>121.0829467087022</v>
+        <v>120.6656622782696</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07209050679795888</v>
+        <v>0.07231897532748348</v>
       </c>
       <c r="T5">
-        <v>0.6071710576895815</v>
+        <v>0.6124474671474244</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.00997143549776</v>
+        <v>49.50747857662331</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07109617631438414</v>
+        <v>0.07101209103474815</v>
       </c>
       <c r="C6">
-        <v>886.9500284330256</v>
+        <v>877.881678350381</v>
       </c>
       <c r="D6">
-        <v>875.5303326733756</v>
+        <v>876.4570586508183</v>
       </c>
       <c r="E6">
-        <v>-856.3273017683971</v>
+        <v>-846.3322257083096</v>
       </c>
       <c r="F6">
-        <v>39.98030424034988</v>
+        <v>49.97538030043735</v>
       </c>
       <c r="G6">
         <v>51.4</v>
@@ -1773,28 +1773,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M6">
-        <v>2.011009303289599</v>
+        <v>2.513761629111999</v>
       </c>
       <c r="N6">
-        <v>97.54899069671039</v>
+        <v>97.04623837088799</v>
       </c>
       <c r="O6">
-        <v>16.58332841844077</v>
+        <v>16.49786052305096</v>
       </c>
       <c r="P6">
-        <v>80.96566227826962</v>
+        <v>80.54837784783703</v>
       </c>
       <c r="Q6">
-        <v>120.6656622782696</v>
+        <v>120.248377847837</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07231897532748348</v>
+        <v>0.07255225372078752</v>
       </c>
       <c r="T6">
-        <v>0.6124474671474244</v>
+        <v>0.6178349589096428</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.50747857662331</v>
+        <v>39.60598286129865</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07101209103474815</v>
+        <v>0.07092800575511217</v>
       </c>
       <c r="C7">
-        <v>877.881678350381</v>
+        <v>868.815292176942</v>
       </c>
       <c r="D7">
-        <v>876.4570586508183</v>
+        <v>877.3857485374668</v>
       </c>
       <c r="E7">
-        <v>-846.3322257083096</v>
+        <v>-836.3371496482221</v>
       </c>
       <c r="F7">
-        <v>49.97538030043735</v>
+        <v>59.97045636052482</v>
       </c>
       <c r="G7">
         <v>51.4</v>
@@ -1855,28 +1855,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M7">
-        <v>2.513761629111999</v>
+        <v>3.016513954934398</v>
       </c>
       <c r="N7">
-        <v>97.04623837088799</v>
+        <v>96.54348604506559</v>
       </c>
       <c r="O7">
-        <v>16.49786052305096</v>
+        <v>16.41239262766115</v>
       </c>
       <c r="P7">
-        <v>80.54837784783703</v>
+        <v>80.13109341740444</v>
       </c>
       <c r="Q7">
-        <v>120.248377847837</v>
+        <v>119.8310934174044</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07255225372078752</v>
+        <v>0.07279049548416189</v>
       </c>
       <c r="T7">
-        <v>0.6178349589096428</v>
+        <v>0.6233370781561638</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.60598286129865</v>
+        <v>33.00498571774887</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07092800575511217</v>
+        <v>0.0708439204754762</v>
       </c>
       <c r="C8">
-        <v>868.815292176942</v>
+        <v>859.750876162178</v>
       </c>
       <c r="D8">
-        <v>877.3857485374668</v>
+        <v>878.3164085827902</v>
       </c>
       <c r="E8">
-        <v>-836.3371496482221</v>
+        <v>-826.3420735881347</v>
       </c>
       <c r="F8">
-        <v>59.97045636052481</v>
+        <v>69.96553242061228</v>
       </c>
       <c r="G8">
         <v>51.4</v>
@@ -1937,28 +1937,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M8">
-        <v>3.016513954934398</v>
+        <v>3.519266280756797</v>
       </c>
       <c r="N8">
-        <v>96.54348604506559</v>
+        <v>96.04073371924319</v>
       </c>
       <c r="O8">
-        <v>16.41239262766115</v>
+        <v>16.32692473227134</v>
       </c>
       <c r="P8">
-        <v>80.13109341740444</v>
+        <v>79.71380898697186</v>
       </c>
       <c r="Q8">
-        <v>119.8310934174044</v>
+        <v>119.4138089869719</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07279049548416189</v>
+        <v>0.0730338607263185</v>
       </c>
       <c r="T8">
-        <v>0.6233370781561638</v>
+        <v>0.6289575225477713</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.00498571774888</v>
+        <v>28.28998775807047</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0708439204754762</v>
+        <v>0.07075983519584023</v>
       </c>
       <c r="C9">
-        <v>859.750876162178</v>
+        <v>850.6884365821029</v>
       </c>
       <c r="D9">
-        <v>878.3164085827902</v>
+        <v>879.2490450628027</v>
       </c>
       <c r="E9">
-        <v>-826.3420735881347</v>
+        <v>-816.3469975280472</v>
       </c>
       <c r="F9">
-        <v>69.96553242061229</v>
+        <v>79.96060848069976</v>
       </c>
       <c r="G9">
         <v>51.4</v>
@@ -2019,28 +2019,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M9">
-        <v>3.519266280756798</v>
+        <v>4.022018606579198</v>
       </c>
       <c r="N9">
-        <v>96.04073371924319</v>
+        <v>95.53798139342079</v>
       </c>
       <c r="O9">
-        <v>16.32692473227134</v>
+        <v>16.24145683688154</v>
       </c>
       <c r="P9">
-        <v>79.71380898697186</v>
+        <v>79.29652455653925</v>
       </c>
       <c r="Q9">
-        <v>119.4138089869719</v>
+        <v>118.9965245565393</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0730338607263185</v>
+        <v>0.07328251651721764</v>
       </c>
       <c r="T9">
-        <v>0.6289575225477713</v>
+        <v>0.6347001505131094</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.28998775807046</v>
+        <v>24.75373928831166</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07075983519584023</v>
+        <v>0.07067574991620426</v>
       </c>
       <c r="C10">
-        <v>850.6884365821029</v>
+        <v>841.6279797394145</v>
       </c>
       <c r="D10">
-        <v>879.2490450628027</v>
+        <v>880.1836642802018</v>
       </c>
       <c r="E10">
-        <v>-816.3469975280472</v>
+        <v>-806.3519214679598</v>
       </c>
       <c r="F10">
-        <v>79.96060848069976</v>
+        <v>89.95568454078722</v>
       </c>
       <c r="G10">
         <v>51.4</v>
@@ -2101,28 +2101,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M10">
-        <v>4.022018606579198</v>
+        <v>4.524770932401597</v>
       </c>
       <c r="N10">
-        <v>95.53798139342079</v>
+        <v>95.03522906759839</v>
       </c>
       <c r="O10">
-        <v>16.24145683688154</v>
+        <v>16.15598894149173</v>
       </c>
       <c r="P10">
-        <v>79.29652455653925</v>
+        <v>78.87924012610667</v>
       </c>
       <c r="Q10">
-        <v>118.9965245565393</v>
+        <v>118.5792401261067</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07328251651721764</v>
+        <v>0.07353663727055412</v>
       </c>
       <c r="T10">
-        <v>0.6347001505131094</v>
+        <v>0.6405689900820812</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.75373928831166</v>
+        <v>22.00332381183259</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07067574991620426</v>
+        <v>0.07059166463656827</v>
       </c>
       <c r="C11">
-        <v>841.6279797394145</v>
+        <v>832.5695119636388</v>
       </c>
       <c r="D11">
-        <v>880.1836642802018</v>
+        <v>881.1202725645135</v>
       </c>
       <c r="E11">
-        <v>-806.3519214679598</v>
+        <v>-796.3568454078722</v>
       </c>
       <c r="F11">
-        <v>89.95568454078722</v>
+        <v>99.95076060087469</v>
       </c>
       <c r="G11">
         <v>51.4</v>
@@ -2183,28 +2183,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M11">
-        <v>4.524770932401597</v>
+        <v>5.027523258223996</v>
       </c>
       <c r="N11">
-        <v>95.03522906759839</v>
+        <v>94.53247674177599</v>
       </c>
       <c r="O11">
-        <v>16.15598894149173</v>
+        <v>16.07052104610192</v>
       </c>
       <c r="P11">
-        <v>78.87924012610667</v>
+        <v>78.46195569567408</v>
       </c>
       <c r="Q11">
-        <v>118.5792401261067</v>
+        <v>118.1619556956741</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07353663727055412</v>
+        <v>0.07379640515174252</v>
       </c>
       <c r="T11">
-        <v>0.6405689900820812</v>
+        <v>0.6465682483081413</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.00332381183259</v>
+        <v>19.80299143064933</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07059166463656827</v>
+        <v>0.07050757935693229</v>
       </c>
       <c r="C12">
-        <v>832.5695119636388</v>
+        <v>823.5130396112703</v>
       </c>
       <c r="D12">
-        <v>881.1202725645135</v>
+        <v>882.0588762722325</v>
       </c>
       <c r="E12">
-        <v>-796.3568454078722</v>
+        <v>-786.3617693477847</v>
       </c>
       <c r="F12">
-        <v>99.9507606008747</v>
+        <v>109.9458366609622</v>
       </c>
       <c r="G12">
         <v>51.4</v>
@@ -2265,28 +2265,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M12">
-        <v>5.027523258223997</v>
+        <v>5.530275584046397</v>
       </c>
       <c r="N12">
-        <v>94.53247674177599</v>
+        <v>94.02972441595359</v>
       </c>
       <c r="O12">
-        <v>16.07052104610192</v>
+        <v>15.98505315071211</v>
       </c>
       <c r="P12">
-        <v>78.46195569567408</v>
+        <v>78.04467126524148</v>
       </c>
       <c r="Q12">
-        <v>118.1619556956741</v>
+        <v>117.7446712652415</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07379640515174252</v>
+        <v>0.07406201051340706</v>
       </c>
       <c r="T12">
-        <v>0.6465682483081413</v>
+        <v>0.6527023213257983</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.80299143064932</v>
+        <v>18.00271948240848</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07050757935693229</v>
+        <v>0.07042349407729631</v>
       </c>
       <c r="C13">
-        <v>823.5130396112703</v>
+        <v>814.4585690659183</v>
       </c>
       <c r="D13">
-        <v>882.0588762722325</v>
+        <v>882.9994817869679</v>
       </c>
       <c r="E13">
-        <v>-786.3617693477847</v>
+        <v>-776.3666932876973</v>
       </c>
       <c r="F13">
-        <v>109.9458366609622</v>
+        <v>119.9409127210496</v>
       </c>
       <c r="G13">
         <v>51.4</v>
@@ -2347,28 +2347,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M13">
-        <v>5.530275584046397</v>
+        <v>6.033027909868796</v>
       </c>
       <c r="N13">
-        <v>94.02972441595359</v>
+        <v>93.5269720901312</v>
       </c>
       <c r="O13">
-        <v>15.98505315071211</v>
+        <v>15.8995852553223</v>
       </c>
       <c r="P13">
-        <v>78.04467126524148</v>
+        <v>77.62738683480889</v>
       </c>
       <c r="Q13">
-        <v>117.7446712652415</v>
+        <v>117.3273868348089</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07406201051340706</v>
+        <v>0.074333652360564</v>
       </c>
       <c r="T13">
-        <v>0.6527023213257983</v>
+        <v>0.6589758050938567</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.00271948240848</v>
+        <v>16.50249285887444</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07042349407729631</v>
+        <v>0.07033940879766035</v>
       </c>
       <c r="C14">
-        <v>814.4585690659183</v>
+        <v>805.4061067384492</v>
       </c>
       <c r="D14">
-        <v>882.9994817869679</v>
+        <v>883.9420955195864</v>
       </c>
       <c r="E14">
-        <v>-776.3666932876973</v>
+        <v>-766.3716172276098</v>
       </c>
       <c r="F14">
-        <v>119.9409127210496</v>
+        <v>129.9359887811371</v>
       </c>
       <c r="G14">
         <v>51.4</v>
@@ -2429,28 +2429,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M14">
-        <v>6.033027909868796</v>
+        <v>6.535780235691195</v>
       </c>
       <c r="N14">
-        <v>93.5269720901312</v>
+        <v>93.0242197643088</v>
       </c>
       <c r="O14">
-        <v>15.8995852553223</v>
+        <v>15.8141173599325</v>
       </c>
       <c r="P14">
-        <v>77.62738683480889</v>
+        <v>77.2101024043763</v>
       </c>
       <c r="Q14">
-        <v>117.3273868348089</v>
+        <v>116.9101024043763</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.074333652360564</v>
+        <v>0.07461153884788545</v>
       </c>
       <c r="T14">
-        <v>0.6589758050938567</v>
+        <v>0.6653935068795714</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.50249285887444</v>
+        <v>15.23307033126871</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07033940879766035</v>
+        <v>0.07025532351802435</v>
       </c>
       <c r="C15">
-        <v>805.4061067384492</v>
+        <v>796.3556590671352</v>
       </c>
       <c r="D15">
-        <v>883.9420955195864</v>
+        <v>884.8867239083598</v>
       </c>
       <c r="E15">
-        <v>-766.3716172276098</v>
+        <v>-756.3765411675223</v>
       </c>
       <c r="F15">
-        <v>129.9359887811371</v>
+        <v>139.9310648412246</v>
       </c>
       <c r="G15">
         <v>51.4</v>
@@ -2511,28 +2511,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M15">
-        <v>6.535780235691195</v>
+        <v>7.038532561513597</v>
       </c>
       <c r="N15">
-        <v>93.0242197643088</v>
+        <v>92.5214674384864</v>
       </c>
       <c r="O15">
-        <v>15.8141173599325</v>
+        <v>15.72864946454269</v>
       </c>
       <c r="P15">
-        <v>77.2101024043763</v>
+        <v>76.79281797394371</v>
       </c>
       <c r="Q15">
-        <v>116.9101024043763</v>
+        <v>116.4928179739437</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07461153884788545</v>
+        <v>0.07489588781165624</v>
       </c>
       <c r="T15">
-        <v>0.6653935068795714</v>
+        <v>0.6719604575440238</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.23307033126871</v>
+        <v>14.14499387903523</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07025532351802435</v>
+        <v>0.07017123823838838</v>
       </c>
       <c r="C16">
-        <v>796.3556590671352</v>
+        <v>787.307232517797</v>
       </c>
       <c r="D16">
-        <v>884.8867239083598</v>
+        <v>885.8333734191092</v>
       </c>
       <c r="E16">
-        <v>-756.3765411675223</v>
+        <v>-746.3814651074349</v>
       </c>
       <c r="F16">
-        <v>139.9310648412246</v>
+        <v>149.9261409013121</v>
       </c>
       <c r="G16">
         <v>51.4</v>
@@ -2593,28 +2593,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M16">
-        <v>7.038532561513597</v>
+        <v>7.541284887335997</v>
       </c>
       <c r="N16">
-        <v>92.5214674384864</v>
+        <v>92.018715112664</v>
       </c>
       <c r="O16">
-        <v>15.72864946454269</v>
+        <v>15.64318156915288</v>
       </c>
       <c r="P16">
-        <v>76.79281797394371</v>
+        <v>76.37553354351111</v>
       </c>
       <c r="Q16">
-        <v>116.4928179739437</v>
+        <v>116.0755335435111</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07489588781165624</v>
+        <v>0.07518692733928045</v>
       </c>
       <c r="T16">
-        <v>0.6719604575440238</v>
+        <v>0.6786819246946986</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.14499387903523</v>
+        <v>13.20199428709955</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07017123823838838</v>
+        <v>0.07028635295875241</v>
       </c>
       <c r="C17">
-        <v>787.3072325177972</v>
+        <v>776.0166819515219</v>
       </c>
       <c r="D17">
-        <v>885.8333734191092</v>
+        <v>884.5378989129215</v>
       </c>
       <c r="E17">
-        <v>-746.3814651074349</v>
+        <v>-736.3863890473474</v>
       </c>
       <c r="F17">
-        <v>149.926140901312</v>
+        <v>159.9212169613995</v>
       </c>
       <c r="G17">
         <v>51.4</v>
@@ -2675,45 +2675,45 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M17">
-        <v>7.541284887335995</v>
+        <v>8.283919038600494</v>
       </c>
       <c r="N17">
-        <v>92.018715112664</v>
+        <v>91.27608096139949</v>
       </c>
       <c r="O17">
-        <v>15.64318156915288</v>
+        <v>15.51693376343791</v>
       </c>
       <c r="P17">
-        <v>76.37553354351111</v>
+        <v>75.75914719796157</v>
       </c>
       <c r="Q17">
-        <v>116.0755335435111</v>
+        <v>115.4591471979616</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07518692733928045</v>
+        <v>0.07548489637946715</v>
       </c>
       <c r="T17">
-        <v>0.6786819246946986</v>
+        <v>0.6855634267775322</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.17</v>
       </c>
       <c r="W17">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.20199428709955</v>
+        <v>12.01846608303162</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07028635295875241</v>
+        <v>0.07021471767911643</v>
       </c>
       <c r="C18">
-        <v>776.0166819515219</v>
+        <v>766.8273270944372</v>
       </c>
       <c r="D18">
-        <v>884.5378989129215</v>
+        <v>885.3436201159243</v>
       </c>
       <c r="E18">
-        <v>-736.3863890473474</v>
+        <v>-726.3913129872599</v>
       </c>
       <c r="F18">
-        <v>159.9212169613995</v>
+        <v>169.916293021487</v>
       </c>
       <c r="G18">
         <v>51.4</v>
@@ -2757,28 +2757,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M18">
-        <v>8.283919038600494</v>
+        <v>8.801663978513027</v>
       </c>
       <c r="N18">
-        <v>91.27608096139949</v>
+        <v>90.75833602148697</v>
       </c>
       <c r="O18">
-        <v>15.51693376343791</v>
+        <v>15.42891712365279</v>
       </c>
       <c r="P18">
-        <v>75.75914719796157</v>
+        <v>75.32941889783419</v>
       </c>
       <c r="Q18">
-        <v>115.4591471979616</v>
+        <v>115.0294188978342</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07548489637946715</v>
+        <v>0.07579004539652581</v>
       </c>
       <c r="T18">
-        <v>0.6855634267775322</v>
+        <v>0.6926107481876631</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.01846608303162</v>
+        <v>11.31149748991212</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07021471767911643</v>
+        <v>0.07014308239948044</v>
       </c>
       <c r="C19">
-        <v>766.8273270944372</v>
+        <v>757.6394414305613</v>
       </c>
       <c r="D19">
-        <v>885.3436201159243</v>
+        <v>886.1508105121358</v>
       </c>
       <c r="E19">
-        <v>-726.3913129872599</v>
+        <v>-716.3962369271725</v>
       </c>
       <c r="F19">
-        <v>169.916293021487</v>
+        <v>179.9113690815745</v>
       </c>
       <c r="G19">
         <v>51.4</v>
@@ -2839,28 +2839,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M19">
-        <v>8.801663978513027</v>
+        <v>9.319408918425557</v>
       </c>
       <c r="N19">
-        <v>90.75833602148697</v>
+        <v>90.24059108157444</v>
       </c>
       <c r="O19">
-        <v>15.42891712365279</v>
+        <v>15.34090048386765</v>
       </c>
       <c r="P19">
-        <v>75.32941889783419</v>
+        <v>74.89969059770678</v>
       </c>
       <c r="Q19">
-        <v>115.0294188978342</v>
+        <v>114.5996905977068</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07579004539652581</v>
+        <v>0.07610263707253713</v>
       </c>
       <c r="T19">
-        <v>0.6926107481876631</v>
+        <v>0.6998299554858459</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.31149748991212</v>
+        <v>10.68308096269478</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07014308239948044</v>
+        <v>0.07007144711984448</v>
       </c>
       <c r="C20">
-        <v>757.6394414305613</v>
+        <v>748.4530289820641</v>
       </c>
       <c r="D20">
-        <v>886.1508105121358</v>
+        <v>886.9594741237261</v>
       </c>
       <c r="E20">
-        <v>-716.3962369271725</v>
+        <v>-706.401160867085</v>
       </c>
       <c r="F20">
-        <v>179.9113690815744</v>
+        <v>189.9064451416619</v>
       </c>
       <c r="G20">
         <v>51.4</v>
@@ -2921,28 +2921,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M20">
-        <v>9.319408918425555</v>
+        <v>9.837153858338088</v>
       </c>
       <c r="N20">
-        <v>90.24059108157444</v>
+        <v>89.7228461416619</v>
       </c>
       <c r="O20">
-        <v>15.34090048386765</v>
+        <v>15.25288384408253</v>
       </c>
       <c r="P20">
-        <v>74.89969059770678</v>
+        <v>74.46996229757937</v>
       </c>
       <c r="Q20">
-        <v>114.5996905977068</v>
+        <v>114.1699622975794</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07610263707253713</v>
+        <v>0.07642294706153638</v>
       </c>
       <c r="T20">
-        <v>0.6998299554858459</v>
+        <v>0.7072274148160828</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.68308096269478</v>
+        <v>10.12081354360558</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07007144711984448</v>
+        <v>0.07028201184020849</v>
       </c>
       <c r="C21">
-        <v>748.4530289820641</v>
+        <v>736.0851629025278</v>
       </c>
       <c r="D21">
-        <v>886.9594741237261</v>
+        <v>884.5866841042773</v>
       </c>
       <c r="E21">
-        <v>-706.401160867085</v>
+        <v>-696.4060848069976</v>
       </c>
       <c r="F21">
-        <v>189.9064451416619</v>
+        <v>199.9015212017494</v>
       </c>
       <c r="G21">
         <v>51.4</v>
@@ -3003,45 +3003,45 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M21">
-        <v>9.837153858338088</v>
+        <v>10.69473138429359</v>
       </c>
       <c r="N21">
-        <v>89.7228461416619</v>
+        <v>88.8652686157064</v>
       </c>
       <c r="O21">
-        <v>15.25288384408253</v>
+        <v>15.10709566467009</v>
       </c>
       <c r="P21">
-        <v>74.46996229757937</v>
+        <v>73.75817295103631</v>
       </c>
       <c r="Q21">
-        <v>114.1699622975794</v>
+        <v>113.4581729510363</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07642294706153638</v>
+        <v>0.07675126480026062</v>
       </c>
       <c r="T21">
-        <v>0.7072274148160828</v>
+        <v>0.7148098106295754</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.17</v>
       </c>
       <c r="W21">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.12081354360558</v>
+        <v>9.309256719267859</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07028201184020849</v>
+        <v>0.07022448656057251</v>
       </c>
       <c r="C22">
-        <v>736.0851629025278</v>
+        <v>726.7370604707884</v>
       </c>
       <c r="D22">
-        <v>884.5866841042773</v>
+        <v>885.2336577326253</v>
       </c>
       <c r="E22">
-        <v>-696.4060848069976</v>
+        <v>-686.4110087469101</v>
       </c>
       <c r="F22">
-        <v>199.9015212017494</v>
+        <v>209.8965972618369</v>
       </c>
       <c r="G22">
         <v>51.4</v>
@@ -3085,28 +3085,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M22">
-        <v>10.69473138429359</v>
+        <v>11.22946795350827</v>
       </c>
       <c r="N22">
-        <v>88.8652686157064</v>
+        <v>88.33053204649171</v>
       </c>
       <c r="O22">
-        <v>15.10709566467009</v>
+        <v>15.01619044790359</v>
       </c>
       <c r="P22">
-        <v>73.75817295103631</v>
+        <v>73.31434159858811</v>
       </c>
       <c r="Q22">
-        <v>113.4581729510363</v>
+        <v>113.0143415985881</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07675126480026062</v>
+        <v>0.07708789438047153</v>
       </c>
       <c r="T22">
-        <v>0.7148098106295754</v>
+        <v>0.7225841658307514</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.309256719267859</v>
+        <v>8.865958780255104</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07022448656057251</v>
+        <v>0.07016696128093654</v>
       </c>
       <c r="C23">
-        <v>726.7370604707884</v>
+        <v>717.3899051056206</v>
       </c>
       <c r="D23">
-        <v>885.2336577326253</v>
+        <v>885.881578427545</v>
       </c>
       <c r="E23">
-        <v>-686.4110087469101</v>
+        <v>-676.4159326868225</v>
       </c>
       <c r="F23">
-        <v>209.8965972618369</v>
+        <v>219.8916733219243</v>
       </c>
       <c r="G23">
         <v>51.4</v>
@@ -3167,28 +3167,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M23">
-        <v>11.22946795350827</v>
+        <v>11.76420452272295</v>
       </c>
       <c r="N23">
-        <v>88.33053204649171</v>
+        <v>87.79579547727704</v>
       </c>
       <c r="O23">
-        <v>15.01619044790359</v>
+        <v>14.9252852311371</v>
       </c>
       <c r="P23">
-        <v>73.31434159858811</v>
+        <v>72.87051024613994</v>
       </c>
       <c r="Q23">
-        <v>113.0143415985881</v>
+        <v>112.5705102461399</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07708789438047153</v>
+        <v>0.07743315548838017</v>
       </c>
       <c r="T23">
-        <v>0.7225841658307514</v>
+        <v>0.7305578634729832</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.865958780255106</v>
+        <v>8.462960653879872</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07016696128093654</v>
+        <v>0.07010943600130055</v>
       </c>
       <c r="C24">
-        <v>717.3899051056206</v>
+        <v>708.0436988880808</v>
       </c>
       <c r="D24">
-        <v>885.881578427545</v>
+        <v>886.5304482700926</v>
       </c>
       <c r="E24">
-        <v>-676.4159326868225</v>
+        <v>-666.4208566267351</v>
       </c>
       <c r="F24">
-        <v>219.8916733219243</v>
+        <v>229.8867493820118</v>
       </c>
       <c r="G24">
         <v>51.4</v>
@@ -3249,28 +3249,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M24">
-        <v>11.76420452272295</v>
+        <v>12.29894109193763</v>
       </c>
       <c r="N24">
-        <v>87.79579547727704</v>
+        <v>87.26105890806235</v>
       </c>
       <c r="O24">
-        <v>14.9252852311371</v>
+        <v>14.8343800143706</v>
       </c>
       <c r="P24">
-        <v>72.87051024613994</v>
+        <v>72.42667889369176</v>
       </c>
       <c r="Q24">
-        <v>112.5705102461399</v>
+        <v>112.1266788936918</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07743315548838017</v>
+        <v>0.07778738441727345</v>
       </c>
       <c r="T24">
-        <v>0.7305578634729832</v>
+        <v>0.7387386701448834</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.462960653879872</v>
+        <v>8.095005842841616</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07010943600130055</v>
+        <v>0.07005191072166458</v>
       </c>
       <c r="C25">
-        <v>708.0436988880808</v>
+        <v>698.6984439053257</v>
       </c>
       <c r="D25">
-        <v>886.5304482700926</v>
+        <v>887.180269347425</v>
       </c>
       <c r="E25">
-        <v>-666.4208566267351</v>
+        <v>-656.4257805666476</v>
       </c>
       <c r="F25">
-        <v>229.8867493820118</v>
+        <v>239.8818254420993</v>
       </c>
       <c r="G25">
         <v>51.4</v>
@@ -3331,28 +3331,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M25">
-        <v>12.29894109193763</v>
+        <v>12.83367766115231</v>
       </c>
       <c r="N25">
-        <v>87.26105890806235</v>
+        <v>86.72632233884768</v>
       </c>
       <c r="O25">
-        <v>14.8343800143706</v>
+        <v>14.74347479760411</v>
       </c>
       <c r="P25">
-        <v>72.42667889369176</v>
+        <v>71.98284754124357</v>
       </c>
       <c r="Q25">
-        <v>112.1266788936918</v>
+        <v>111.6828475412436</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07778738441727345</v>
+        <v>0.07815093516008498</v>
       </c>
       <c r="T25">
-        <v>0.7387386701448834</v>
+        <v>0.7471347612028861</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.095005842841616</v>
+        <v>7.757713932723217</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07005191072166458</v>
+        <v>0.0701603854420286</v>
       </c>
       <c r="C26">
-        <v>698.6984439053257</v>
+        <v>687.478802550557</v>
       </c>
       <c r="D26">
-        <v>887.180269347425</v>
+        <v>885.9557040527437</v>
       </c>
       <c r="E26">
-        <v>-656.4257805666476</v>
+        <v>-646.4307045065602</v>
       </c>
       <c r="F26">
-        <v>239.8818254420993</v>
+        <v>249.8769015021867</v>
       </c>
       <c r="G26">
         <v>51.4</v>
@@ -3413,45 +3413,45 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M26">
-        <v>12.83367766115231</v>
+        <v>13.56831575156874</v>
       </c>
       <c r="N26">
-        <v>86.72632233884768</v>
+        <v>85.99168424843126</v>
       </c>
       <c r="O26">
-        <v>14.74347479760411</v>
+        <v>14.61858632223331</v>
       </c>
       <c r="P26">
-        <v>71.98284754124357</v>
+        <v>71.37309792619794</v>
       </c>
       <c r="Q26">
-        <v>111.6828475412436</v>
+        <v>111.0730979261979</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07815093516008498</v>
+        <v>0.07852418058937147</v>
       </c>
       <c r="T26">
-        <v>0.7471347612028861</v>
+        <v>0.7557547480224358</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.17</v>
       </c>
       <c r="W26">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.757713932723218</v>
+        <v>7.337683012608921</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0701603854420286</v>
+        <v>0.07010950016239262</v>
       </c>
       <c r="C27">
-        <v>687.478802550557</v>
+        <v>678.0577464582761</v>
       </c>
       <c r="D27">
-        <v>885.9557040527437</v>
+        <v>886.5297240205504</v>
       </c>
       <c r="E27">
-        <v>-646.4307045065602</v>
+        <v>-636.4356284464727</v>
       </c>
       <c r="F27">
-        <v>249.8769015021867</v>
+        <v>259.8719775622742</v>
       </c>
       <c r="G27">
         <v>51.4</v>
@@ -3495,28 +3495,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M27">
-        <v>13.56831575156874</v>
+        <v>14.11104838163149</v>
       </c>
       <c r="N27">
-        <v>85.99168424843126</v>
+        <v>85.4489516183685</v>
       </c>
       <c r="O27">
-        <v>14.61858632223331</v>
+        <v>14.52632177512265</v>
       </c>
       <c r="P27">
-        <v>71.37309792619794</v>
+        <v>70.92262984324586</v>
       </c>
       <c r="Q27">
-        <v>111.0730979261979</v>
+        <v>110.6226298432459</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07852418058937147</v>
+        <v>0.07890751373296301</v>
       </c>
       <c r="T27">
-        <v>0.7557547480224358</v>
+        <v>0.76460770745873</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.337683012608921</v>
+        <v>7.055464435200886</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07010950016239262</v>
+        <v>0.07005861488275664</v>
       </c>
       <c r="C28">
-        <v>678.0577464582761</v>
+        <v>668.6374346753238</v>
       </c>
       <c r="D28">
-        <v>886.5297240205504</v>
+        <v>887.1044882976855</v>
       </c>
       <c r="E28">
-        <v>-636.4356284464727</v>
+        <v>-626.4405523863852</v>
       </c>
       <c r="F28">
-        <v>259.8719775622742</v>
+        <v>269.8670536223617</v>
       </c>
       <c r="G28">
         <v>51.4</v>
@@ -3577,28 +3577,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M28">
-        <v>14.11104838163149</v>
+        <v>14.65378101169424</v>
       </c>
       <c r="N28">
-        <v>85.4489516183685</v>
+        <v>84.90621898830575</v>
       </c>
       <c r="O28">
-        <v>14.52632177512265</v>
+        <v>14.43405722801198</v>
       </c>
       <c r="P28">
-        <v>70.92262984324586</v>
+        <v>70.47216176029377</v>
       </c>
       <c r="Q28">
-        <v>110.6226298432459</v>
+        <v>110.1721617602938</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07890751373296301</v>
+        <v>0.07930134915446116</v>
       </c>
       <c r="T28">
-        <v>0.76460770745873</v>
+        <v>0.7737032137288952</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.055464435200886</v>
+        <v>6.794150937600852</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07005861488275664</v>
+        <v>0.07000772960312067</v>
       </c>
       <c r="C29">
-        <v>668.6374346753238</v>
+        <v>659.2178686503146</v>
       </c>
       <c r="D29">
-        <v>887.1044882976855</v>
+        <v>887.6799983327637</v>
       </c>
       <c r="E29">
-        <v>-626.4405523863852</v>
+        <v>-616.4454763262977</v>
       </c>
       <c r="F29">
-        <v>269.8670536223617</v>
+        <v>279.8621296824492</v>
       </c>
       <c r="G29">
         <v>51.4</v>
@@ -3659,28 +3659,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M29">
-        <v>14.65378101169424</v>
+        <v>15.19651364175699</v>
       </c>
       <c r="N29">
-        <v>84.90621898830575</v>
+        <v>84.36348635824299</v>
       </c>
       <c r="O29">
-        <v>14.43405722801198</v>
+        <v>14.34179268090131</v>
       </c>
       <c r="P29">
-        <v>70.47216176029377</v>
+        <v>70.02169367734169</v>
       </c>
       <c r="Q29">
-        <v>110.1721617602938</v>
+        <v>109.7216936773417</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07930134915446116</v>
+        <v>0.07970612444877871</v>
       </c>
       <c r="T29">
-        <v>0.7737032137288952</v>
+        <v>0.7830513729510095</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.794150937600852</v>
+        <v>6.551502689829393</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07000772960312067</v>
+        <v>0.06995684432348469</v>
       </c>
       <c r="C30">
-        <v>659.2178686503146</v>
+        <v>649.7990498356248</v>
       </c>
       <c r="D30">
-        <v>887.6799983327637</v>
+        <v>888.2562555781615</v>
       </c>
       <c r="E30">
-        <v>-616.4454763262977</v>
+        <v>-606.4504002662102</v>
       </c>
       <c r="F30">
-        <v>279.8621296824492</v>
+        <v>289.8572057425367</v>
       </c>
       <c r="G30">
         <v>51.4</v>
@@ -3741,28 +3741,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M30">
-        <v>15.19651364175699</v>
+        <v>15.73924627181974</v>
       </c>
       <c r="N30">
-        <v>84.36348635824299</v>
+        <v>83.82075372818025</v>
       </c>
       <c r="O30">
-        <v>14.34179268090131</v>
+        <v>14.24952813379064</v>
       </c>
       <c r="P30">
-        <v>70.02169367734169</v>
+        <v>69.5712255943896</v>
       </c>
       <c r="Q30">
-        <v>109.7216936773417</v>
+        <v>109.2712255943896</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07970612444877871</v>
+        <v>0.08012230186406294</v>
       </c>
       <c r="T30">
-        <v>0.7830513729510095</v>
+        <v>0.7926628606019157</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.551502689829393</v>
+        <v>6.325588803973207</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06995684432348467</v>
+        <v>0.06990595904384871</v>
       </c>
       <c r="C31">
-        <v>649.7990498356249</v>
+        <v>640.3809796874045</v>
       </c>
       <c r="D31">
-        <v>888.2562555781616</v>
+        <v>888.8332614900286</v>
       </c>
       <c r="E31">
-        <v>-606.4504002662103</v>
+        <v>-596.4553242061229</v>
       </c>
       <c r="F31">
-        <v>289.8572057425366</v>
+        <v>299.8522818026241</v>
       </c>
       <c r="G31">
         <v>51.4</v>
@@ -3823,28 +3823,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M31">
-        <v>15.73924627181974</v>
+        <v>16.28197890188249</v>
       </c>
       <c r="N31">
-        <v>83.82075372818025</v>
+        <v>83.27802109811751</v>
       </c>
       <c r="O31">
-        <v>14.24952813379064</v>
+        <v>14.15726358667998</v>
       </c>
       <c r="P31">
-        <v>69.5712255943896</v>
+        <v>69.12075751143753</v>
       </c>
       <c r="Q31">
-        <v>109.2712255943896</v>
+        <v>108.8207575114375</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08012230186406294</v>
+        <v>0.08055037006264101</v>
       </c>
       <c r="T31">
-        <v>0.7926628606019156</v>
+        <v>0.8025489621857048</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.325588803973208</v>
+        <v>6.114735843840768</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06990595904384871</v>
+        <v>0.07011237376421273</v>
       </c>
       <c r="C32">
-        <v>640.3809796874045</v>
+        <v>628.0499301925255</v>
       </c>
       <c r="D32">
-        <v>888.8332614900286</v>
+        <v>886.497288055237</v>
       </c>
       <c r="E32">
-        <v>-596.4553242061229</v>
+        <v>-586.4602481460354</v>
       </c>
       <c r="F32">
-        <v>299.8522818026241</v>
+        <v>309.8473578627115</v>
       </c>
       <c r="G32">
         <v>51.4</v>
@@ -3905,45 +3905,45 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M32">
-        <v>16.28197890188249</v>
+        <v>17.13455888980795</v>
       </c>
       <c r="N32">
-        <v>83.27802109811751</v>
+        <v>82.42544111019204</v>
       </c>
       <c r="O32">
-        <v>14.15726358667998</v>
+        <v>14.01232498873265</v>
       </c>
       <c r="P32">
-        <v>69.12075751143753</v>
+        <v>68.4131161214594</v>
       </c>
       <c r="Q32">
-        <v>108.8207575114375</v>
+        <v>108.1131161214594</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08055037006264101</v>
+        <v>0.08099084603509092</v>
       </c>
       <c r="T32">
-        <v>0.8025489621857048</v>
+        <v>0.8127216174385894</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.17</v>
       </c>
       <c r="W32">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.114735843840768</v>
+        <v>5.810479314948732</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07011237376421273</v>
+        <v>0.07006978848457676</v>
       </c>
       <c r="C33">
-        <v>628.0499301925255</v>
+        <v>618.5357813903626</v>
       </c>
       <c r="D33">
-        <v>886.497288055237</v>
+        <v>886.9782153131616</v>
       </c>
       <c r="E33">
-        <v>-586.4602481460354</v>
+        <v>-576.4651720859479</v>
       </c>
       <c r="F33">
-        <v>309.8473578627115</v>
+        <v>319.842433922799</v>
       </c>
       <c r="G33">
         <v>51.4</v>
@@ -3987,28 +3987,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M33">
-        <v>17.13455888980795</v>
+        <v>17.68728659593079</v>
       </c>
       <c r="N33">
-        <v>82.42544111019204</v>
+        <v>81.8727134040692</v>
       </c>
       <c r="O33">
-        <v>14.01232498873265</v>
+        <v>13.91836127869177</v>
       </c>
       <c r="P33">
-        <v>68.4131161214594</v>
+        <v>67.95435212537744</v>
       </c>
       <c r="Q33">
-        <v>108.1131161214594</v>
+        <v>107.6543521253774</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08099084603509092</v>
+        <v>0.08144427718320112</v>
       </c>
       <c r="T33">
-        <v>0.8127216174385894</v>
+        <v>0.8231934684342059</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.810479314948732</v>
+        <v>5.628901836356583</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07006978848457676</v>
+        <v>0.07002720320494078</v>
       </c>
       <c r="C34">
-        <v>618.5357813903626</v>
+        <v>609.0221546802009</v>
       </c>
       <c r="D34">
-        <v>886.9782153131616</v>
+        <v>887.4596646630874</v>
       </c>
       <c r="E34">
-        <v>-576.4651720859479</v>
+        <v>-566.4700960258604</v>
       </c>
       <c r="F34">
-        <v>319.842433922799</v>
+        <v>329.8375099828865</v>
       </c>
       <c r="G34">
         <v>51.4</v>
@@ -4069,28 +4069,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M34">
-        <v>17.68728659593079</v>
+        <v>18.24001430205362</v>
       </c>
       <c r="N34">
-        <v>81.8727134040692</v>
+        <v>81.31998569794636</v>
       </c>
       <c r="O34">
-        <v>13.91836127869177</v>
+        <v>13.82439756865088</v>
       </c>
       <c r="P34">
-        <v>67.95435212537744</v>
+        <v>67.49558812929548</v>
       </c>
       <c r="Q34">
-        <v>107.6543521253774</v>
+        <v>107.1955881292955</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08144427718320112</v>
+        <v>0.08191124358946386</v>
       </c>
       <c r="T34">
-        <v>0.8231934684342059</v>
+        <v>0.8339779119968558</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.628901836356583</v>
+        <v>5.458329053436687</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07002720320494078</v>
+        <v>0.0699846179253048</v>
       </c>
       <c r="C35">
-        <v>609.0221546802009</v>
+        <v>599.5090509126724</v>
       </c>
       <c r="D35">
-        <v>887.4596646630874</v>
+        <v>887.9416369556463</v>
       </c>
       <c r="E35">
-        <v>-566.4700960258604</v>
+        <v>-556.4750199657728</v>
       </c>
       <c r="F35">
-        <v>329.8375099828865</v>
+        <v>339.832586042974</v>
       </c>
       <c r="G35">
         <v>51.4</v>
@@ -4151,28 +4151,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M35">
-        <v>18.24001430205362</v>
+        <v>18.79274200817646</v>
       </c>
       <c r="N35">
-        <v>81.31998569794636</v>
+        <v>80.76725799182353</v>
       </c>
       <c r="O35">
-        <v>13.82439756865088</v>
+        <v>13.73043385861</v>
       </c>
       <c r="P35">
-        <v>67.49558812929548</v>
+        <v>67.03682413321353</v>
       </c>
       <c r="Q35">
-        <v>107.1955881292955</v>
+        <v>106.7368241332135</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08191124358946386</v>
+        <v>0.08239236049288606</v>
       </c>
       <c r="T35">
-        <v>0.8339779119968558</v>
+        <v>0.845089156879586</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.458329053436687</v>
+        <v>5.297789963629724</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0699846179253048</v>
+        <v>0.06994203264566883</v>
       </c>
       <c r="C36">
-        <v>599.5090509126724</v>
+        <v>589.996470940258</v>
       </c>
       <c r="D36">
-        <v>887.9416369556463</v>
+        <v>888.4241330433194</v>
       </c>
       <c r="E36">
-        <v>-556.4750199657728</v>
+        <v>-546.4799439056854</v>
       </c>
       <c r="F36">
-        <v>339.832586042974</v>
+        <v>349.8276621030615</v>
       </c>
       <c r="G36">
         <v>51.4</v>
@@ -4233,28 +4233,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M36">
-        <v>18.79274200817646</v>
+        <v>19.3454697142993</v>
       </c>
       <c r="N36">
-        <v>80.76725799182353</v>
+        <v>80.21453028570069</v>
       </c>
       <c r="O36">
-        <v>13.73043385861</v>
+        <v>13.63647014856912</v>
       </c>
       <c r="P36">
-        <v>67.03682413321353</v>
+        <v>66.57806013713157</v>
       </c>
       <c r="Q36">
-        <v>106.7368241332135</v>
+        <v>106.2780601371316</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08239236049288606</v>
+        <v>0.08288828099333666</v>
       </c>
       <c r="T36">
-        <v>0.845089156879586</v>
+        <v>0.8565422862202461</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.297789963629724</v>
+        <v>5.146424536097448</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06994203264566883</v>
+        <v>0.06989944736603285</v>
       </c>
       <c r="C37">
-        <v>589.996470940258</v>
+        <v>580.4844156172926</v>
       </c>
       <c r="D37">
-        <v>888.4241330433194</v>
+        <v>888.9071537804416</v>
       </c>
       <c r="E37">
-        <v>-546.4799439056854</v>
+        <v>-536.484867845598</v>
       </c>
       <c r="F37">
-        <v>349.8276621030615</v>
+        <v>359.8227381631489</v>
       </c>
       <c r="G37">
         <v>51.4</v>
@@ -4315,28 +4315,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M37">
-        <v>19.3454697142993</v>
+        <v>19.89819742042214</v>
       </c>
       <c r="N37">
-        <v>80.21453028570069</v>
+        <v>79.66180257957785</v>
       </c>
       <c r="O37">
-        <v>13.63647014856912</v>
+        <v>13.54250643852824</v>
       </c>
       <c r="P37">
-        <v>66.57806013713157</v>
+        <v>66.11929614104962</v>
       </c>
       <c r="Q37">
-        <v>106.2780601371316</v>
+        <v>105.8192961410496</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08288828099333666</v>
+        <v>0.08339969900942633</v>
       </c>
       <c r="T37">
-        <v>0.8565422862202461</v>
+        <v>0.8683533258528021</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.146424536097448</v>
+        <v>5.00346829898363</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06989944736603285</v>
+        <v>0.06985686208639688</v>
       </c>
       <c r="C38">
-        <v>580.4844156172927</v>
+        <v>570.97288579997</v>
       </c>
       <c r="D38">
-        <v>888.9071537804416</v>
+        <v>889.3907000232064</v>
       </c>
       <c r="E38">
-        <v>-536.484867845598</v>
+        <v>-526.4897917855105</v>
       </c>
       <c r="F38">
-        <v>359.8227381631489</v>
+        <v>369.8178142232364</v>
       </c>
       <c r="G38">
         <v>51.4</v>
@@ -4397,28 +4397,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M38">
-        <v>19.89819742042213</v>
+        <v>20.45092512654497</v>
       </c>
       <c r="N38">
-        <v>79.66180257957785</v>
+        <v>79.10907487345501</v>
       </c>
       <c r="O38">
-        <v>13.54250643852824</v>
+        <v>13.44854272848735</v>
       </c>
       <c r="P38">
-        <v>66.11929614104962</v>
+        <v>65.66053214496766</v>
       </c>
       <c r="Q38">
-        <v>105.8192961410496</v>
+        <v>105.3605321449677</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08339969900942631</v>
+        <v>0.08392735251809028</v>
       </c>
       <c r="T38">
-        <v>0.8683533258528019</v>
+        <v>0.8805393191244867</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.003468298983631</v>
+        <v>4.868239426038126</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06985686208639688</v>
+        <v>0.06981427680676089</v>
       </c>
       <c r="C39">
-        <v>570.97288579997</v>
+        <v>561.4618823463479</v>
       </c>
       <c r="D39">
-        <v>889.3907000232064</v>
+        <v>889.8747726296718</v>
       </c>
       <c r="E39">
-        <v>-526.4897917855105</v>
+        <v>-516.494715725423</v>
       </c>
       <c r="F39">
-        <v>369.8178142232364</v>
+        <v>379.8128902833238</v>
       </c>
       <c r="G39">
         <v>51.4</v>
@@ -4479,28 +4479,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M39">
-        <v>20.45092512654497</v>
+        <v>21.00365283266781</v>
       </c>
       <c r="N39">
-        <v>79.10907487345501</v>
+        <v>78.55634716733218</v>
       </c>
       <c r="O39">
-        <v>13.44854272848735</v>
+        <v>13.35457901844647</v>
       </c>
       <c r="P39">
-        <v>65.66053214496766</v>
+        <v>65.20176814888571</v>
       </c>
       <c r="Q39">
-        <v>105.3605321449677</v>
+        <v>104.9017681488857</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08392735251809028</v>
+        <v>0.08447202710767886</v>
       </c>
       <c r="T39">
-        <v>0.8805393191244867</v>
+        <v>0.8931184089533224</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.868239426038126</v>
+        <v>4.740127862195018</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06981427680676089</v>
+        <v>0.06977169152712491</v>
       </c>
       <c r="C40">
-        <v>561.4618823463479</v>
+        <v>551.9514061163536</v>
       </c>
       <c r="D40">
-        <v>889.8747726296718</v>
+        <v>890.3593724597649</v>
       </c>
       <c r="E40">
-        <v>-516.494715725423</v>
+        <v>-506.4996396653356</v>
       </c>
       <c r="F40">
-        <v>379.8128902833238</v>
+        <v>389.8079663434114</v>
       </c>
       <c r="G40">
         <v>51.4</v>
@@ -4561,28 +4561,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M40">
-        <v>21.00365283266781</v>
+        <v>21.55638053879065</v>
       </c>
       <c r="N40">
-        <v>78.55634716733218</v>
+        <v>78.00361946120934</v>
       </c>
       <c r="O40">
-        <v>13.35457901844647</v>
+        <v>13.26061530840559</v>
       </c>
       <c r="P40">
-        <v>65.20176814888571</v>
+        <v>64.74300415280375</v>
       </c>
       <c r="Q40">
-        <v>104.9017681488857</v>
+        <v>104.4430041528038</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08447202710767886</v>
+        <v>0.08503455988053264</v>
       </c>
       <c r="T40">
-        <v>0.8931184089533224</v>
+        <v>0.9061099279568741</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.740127862195018</v>
+        <v>4.618586122138735</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06977169152712491</v>
+        <v>0.06972910624748893</v>
       </c>
       <c r="C41">
-        <v>551.9514061163536</v>
+        <v>542.4414579717878</v>
       </c>
       <c r="D41">
-        <v>890.3593724597649</v>
+        <v>890.8445003752867</v>
       </c>
       <c r="E41">
-        <v>-506.4996396653356</v>
+        <v>-496.5045636052481</v>
       </c>
       <c r="F41">
-        <v>389.8079663434114</v>
+        <v>399.8030424034988</v>
       </c>
       <c r="G41">
         <v>51.4</v>
@@ -4643,28 +4643,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M41">
-        <v>21.55638053879065</v>
+        <v>22.10910824491349</v>
       </c>
       <c r="N41">
-        <v>78.00361946120934</v>
+        <v>77.4508917550865</v>
       </c>
       <c r="O41">
-        <v>13.26061530840559</v>
+        <v>13.16665159836471</v>
       </c>
       <c r="P41">
-        <v>64.74300415280375</v>
+        <v>64.28424015672179</v>
       </c>
       <c r="Q41">
-        <v>104.4430041528038</v>
+        <v>103.9842401567218</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08503455988053264</v>
+        <v>0.08561584374581489</v>
       </c>
       <c r="T41">
-        <v>0.9061099279568741</v>
+        <v>0.9195344975938774</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.618586122138735</v>
+        <v>4.503121469085267</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06972910624748893</v>
+        <v>0.07053727096785296</v>
       </c>
       <c r="C42">
-        <v>542.4414579717878</v>
+        <v>523.3290962742083</v>
       </c>
       <c r="D42">
-        <v>890.8445003752867</v>
+        <v>881.7272147377946</v>
       </c>
       <c r="E42">
-        <v>-496.5045636052481</v>
+        <v>-486.5094875451607</v>
       </c>
       <c r="F42">
-        <v>399.8030424034988</v>
+        <v>409.7981184635863</v>
       </c>
       <c r="G42">
         <v>51.4</v>
@@ -4725,45 +4725,45 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M42">
-        <v>22.10910824491349</v>
+        <v>23.68633124719529</v>
       </c>
       <c r="N42">
-        <v>77.4508917550865</v>
+        <v>75.8736687528047</v>
       </c>
       <c r="O42">
-        <v>13.16665159836471</v>
+        <v>12.8985236879768</v>
       </c>
       <c r="P42">
-        <v>64.28424015672179</v>
+        <v>62.97514506482791</v>
       </c>
       <c r="Q42">
-        <v>103.9842401567218</v>
+        <v>102.6751450648279</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08561584374581489</v>
+        <v>0.08621683214890333</v>
       </c>
       <c r="T42">
-        <v>0.9195344975938774</v>
+        <v>0.9334141373880674</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.17</v>
       </c>
       <c r="W42">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.503121469085267</v>
+        <v>4.20326807731311</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07053727096785296</v>
+        <v>0.07051543568821697</v>
       </c>
       <c r="C43">
-        <v>523.3290962742083</v>
+        <v>513.577900603882</v>
       </c>
       <c r="D43">
-        <v>881.7272147377946</v>
+        <v>881.9710951275557</v>
       </c>
       <c r="E43">
-        <v>-486.5094875451607</v>
+        <v>-476.5144114850731</v>
       </c>
       <c r="F43">
-        <v>409.7981184635863</v>
+        <v>419.7931945236738</v>
       </c>
       <c r="G43">
         <v>51.4</v>
@@ -4807,28 +4807,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M43">
-        <v>23.68633124719529</v>
+        <v>24.26404664346835</v>
       </c>
       <c r="N43">
-        <v>75.8736687528047</v>
+        <v>75.29595335653164</v>
       </c>
       <c r="O43">
-        <v>12.8985236879768</v>
+        <v>12.80031207061038</v>
       </c>
       <c r="P43">
-        <v>62.97514506482791</v>
+        <v>62.49564128592126</v>
       </c>
       <c r="Q43">
-        <v>102.6751450648279</v>
+        <v>102.1956412859213</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08621683214890333</v>
+        <v>0.08683854429002927</v>
       </c>
       <c r="T43">
-        <v>0.9334141373880674</v>
+        <v>0.9477723854510226</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.20326807731311</v>
+        <v>4.103190265948512</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07051543568821698</v>
+        <v>0.07049360040858102</v>
       </c>
       <c r="C44">
-        <v>513.5779006038817</v>
+        <v>503.8268398825488</v>
       </c>
       <c r="D44">
-        <v>881.9710951275555</v>
+        <v>882.21511046631</v>
       </c>
       <c r="E44">
-        <v>-476.5144114850732</v>
+        <v>-466.5193354249857</v>
       </c>
       <c r="F44">
-        <v>419.7931945236737</v>
+        <v>429.7882705837612</v>
       </c>
       <c r="G44">
         <v>51.4</v>
@@ -4889,28 +4889,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M44">
-        <v>24.26404664346834</v>
+        <v>24.8417620397414</v>
       </c>
       <c r="N44">
-        <v>75.29595335653164</v>
+        <v>74.71823796025859</v>
       </c>
       <c r="O44">
-        <v>12.80031207061038</v>
+        <v>12.70210045324396</v>
       </c>
       <c r="P44">
-        <v>62.49564128592126</v>
+        <v>62.01613750701463</v>
       </c>
       <c r="Q44">
-        <v>102.1956412859213</v>
+        <v>101.7161375070146</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08683854429002927</v>
+        <v>0.08748207089224738</v>
       </c>
       <c r="T44">
-        <v>0.9477723854510225</v>
+        <v>0.9626344316916253</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.103190265948513</v>
+        <v>4.00776723650785</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07049360040858102</v>
+        <v>0.07174996512894503</v>
       </c>
       <c r="C45">
-        <v>503.8268398825488</v>
+        <v>480.0077201769134</v>
       </c>
       <c r="D45">
-        <v>882.21511046631</v>
+        <v>868.3910668207621</v>
       </c>
       <c r="E45">
-        <v>-466.5193354249857</v>
+        <v>-456.5242593648982</v>
       </c>
       <c r="F45">
-        <v>429.7882705837612</v>
+        <v>439.7833466438487</v>
       </c>
       <c r="G45">
         <v>51.4</v>
@@ -4971,45 +4971,45 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M45">
-        <v>24.8417620397414</v>
+        <v>26.95871914926792</v>
       </c>
       <c r="N45">
-        <v>74.71823796025859</v>
+        <v>72.60128085073207</v>
       </c>
       <c r="O45">
-        <v>12.70210045324396</v>
+        <v>12.34221774462445</v>
       </c>
       <c r="P45">
-        <v>62.01613750701463</v>
+        <v>60.25906310610762</v>
       </c>
       <c r="Q45">
-        <v>101.7161375070146</v>
+        <v>99.95906310610762</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08748207089224738</v>
+        <v>0.08814858058740183</v>
       </c>
       <c r="T45">
-        <v>0.9626344316916253</v>
+        <v>0.9780272652979638</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.17</v>
       </c>
       <c r="W45">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.00776723650785</v>
+        <v>3.693053792680042</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07174996512894503</v>
+        <v>0.07175717984930904</v>
       </c>
       <c r="C46">
-        <v>480.0077201769134</v>
+        <v>469.9345100114257</v>
       </c>
       <c r="D46">
-        <v>868.3910668207621</v>
+        <v>868.3129327153619</v>
       </c>
       <c r="E46">
-        <v>-456.5242593648982</v>
+        <v>-446.5291833048108</v>
       </c>
       <c r="F46">
-        <v>439.7833466438487</v>
+        <v>449.7784227039361</v>
       </c>
       <c r="G46">
         <v>51.4</v>
@@ -5053,28 +5053,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M46">
-        <v>26.95871914926792</v>
+        <v>27.57141731175129</v>
       </c>
       <c r="N46">
-        <v>72.60128085073207</v>
+        <v>71.9885826882487</v>
       </c>
       <c r="O46">
-        <v>12.34221774462445</v>
+        <v>12.23805905700228</v>
       </c>
       <c r="P46">
-        <v>60.25906310610762</v>
+        <v>59.75052363124642</v>
       </c>
       <c r="Q46">
-        <v>99.95906310610762</v>
+        <v>99.45052363124643</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08814858058740183</v>
+        <v>0.08883932699874372</v>
       </c>
       <c r="T46">
-        <v>0.9780272652979638</v>
+        <v>0.9939798383081692</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.693053792680042</v>
+        <v>3.610985930620485</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07175717984930904</v>
+        <v>0.07176439456967307</v>
       </c>
       <c r="C47">
-        <v>469.9345100114257</v>
+        <v>459.8613139050167</v>
       </c>
       <c r="D47">
-        <v>868.3129327153619</v>
+        <v>868.2348126690404</v>
       </c>
       <c r="E47">
-        <v>-446.5291833048108</v>
+        <v>-436.5341072447233</v>
       </c>
       <c r="F47">
-        <v>449.7784227039361</v>
+        <v>459.7734987640236</v>
       </c>
       <c r="G47">
         <v>51.4</v>
@@ -5135,28 +5135,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M47">
-        <v>27.57141731175129</v>
+        <v>28.18411547423465</v>
       </c>
       <c r="N47">
-        <v>71.9885826882487</v>
+        <v>71.37588452576534</v>
       </c>
       <c r="O47">
-        <v>12.23805905700228</v>
+        <v>12.13390036938011</v>
       </c>
       <c r="P47">
-        <v>59.75052363124642</v>
+        <v>59.24198415638524</v>
       </c>
       <c r="Q47">
-        <v>99.45052363124643</v>
+        <v>98.94198415638525</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08883932699874372</v>
+        <v>0.08955565661050569</v>
       </c>
       <c r="T47">
-        <v>0.9939798383081692</v>
+        <v>1.01052324735579</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.610985930620485</v>
+        <v>3.532486236476562</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07176439456967307</v>
+        <v>0.07286388929003709</v>
       </c>
       <c r="C48">
-        <v>459.8613139050167</v>
+        <v>438.1231305373087</v>
       </c>
       <c r="D48">
-        <v>868.2348126690404</v>
+        <v>856.4917053614198</v>
       </c>
       <c r="E48">
-        <v>-436.5341072447233</v>
+        <v>-426.5390311846358</v>
       </c>
       <c r="F48">
-        <v>459.7734987640236</v>
+        <v>469.7685748241111</v>
       </c>
       <c r="G48">
         <v>51.4</v>
@@ -5217,45 +5217,45 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M48">
-        <v>28.18411547423465</v>
+        <v>30.11216564622552</v>
       </c>
       <c r="N48">
-        <v>71.37588452576534</v>
+        <v>69.44783435377447</v>
       </c>
       <c r="O48">
-        <v>12.13390036938011</v>
+        <v>11.80613184014166</v>
       </c>
       <c r="P48">
-        <v>59.24198415638524</v>
+        <v>57.64170251363281</v>
       </c>
       <c r="Q48">
-        <v>98.94198415638525</v>
+        <v>97.34170251363281</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08955565661050569</v>
+        <v>0.09029901752837187</v>
       </c>
       <c r="T48">
-        <v>1.01052324735579</v>
+        <v>1.027690935990113</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.17</v>
       </c>
       <c r="W48">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.532486236476562</v>
+        <v>3.306304872578288</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07286388929003709</v>
+        <v>0.07289434401040112</v>
       </c>
       <c r="C49">
-        <v>438.1231305373087</v>
+        <v>427.8073036445974</v>
       </c>
       <c r="D49">
-        <v>856.4917053614198</v>
+        <v>856.170954528796</v>
       </c>
       <c r="E49">
-        <v>-426.5390311846358</v>
+        <v>-416.5439551245483</v>
       </c>
       <c r="F49">
-        <v>469.7685748241111</v>
+        <v>479.7636508841986</v>
       </c>
       <c r="G49">
         <v>51.4</v>
@@ -5299,28 +5299,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M49">
-        <v>30.11216564622552</v>
+        <v>30.75285002167713</v>
       </c>
       <c r="N49">
-        <v>69.44783435377447</v>
+        <v>68.80714997832285</v>
       </c>
       <c r="O49">
-        <v>11.80613184014166</v>
+        <v>11.69721549631489</v>
       </c>
       <c r="P49">
-        <v>57.64170251363281</v>
+        <v>57.10993448200797</v>
       </c>
       <c r="Q49">
-        <v>97.34170251363281</v>
+        <v>96.80993448200798</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09029901752837187</v>
+        <v>0.09107096925077138</v>
       </c>
       <c r="T49">
-        <v>1.027690935990113</v>
+        <v>1.04551892034114</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.306304872578288</v>
+        <v>3.237423521066241</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07289434401040111</v>
+        <v>0.07292479873076514</v>
       </c>
       <c r="C50">
-        <v>427.8073036445975</v>
+        <v>417.4917169003477</v>
       </c>
       <c r="D50">
-        <v>856.1709545287961</v>
+        <v>855.8504438446338</v>
       </c>
       <c r="E50">
-        <v>-416.5439551245484</v>
+        <v>-406.5488790644609</v>
       </c>
       <c r="F50">
-        <v>479.7636508841985</v>
+        <v>489.758726944286</v>
       </c>
       <c r="G50">
         <v>51.4</v>
@@ -5381,28 +5381,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M50">
-        <v>30.75285002167713</v>
+        <v>31.39353439712874</v>
       </c>
       <c r="N50">
-        <v>68.80714997832285</v>
+        <v>68.16646560287126</v>
       </c>
       <c r="O50">
-        <v>11.69721549631489</v>
+        <v>11.58829915248811</v>
       </c>
       <c r="P50">
-        <v>57.10993448200797</v>
+        <v>56.57816645038314</v>
       </c>
       <c r="Q50">
-        <v>96.80993448200798</v>
+        <v>96.27816645038314</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09107096925077138</v>
+        <v>0.09187319358973556</v>
       </c>
       <c r="T50">
-        <v>1.04551892034114</v>
+        <v>1.064046041333385</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.237423521066241</v>
+        <v>3.171353653289379</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07292479873076514</v>
+        <v>0.07295525345112916</v>
       </c>
       <c r="C51">
-        <v>417.4917169003477</v>
+        <v>407.1763700349593</v>
       </c>
       <c r="D51">
-        <v>855.8504438446338</v>
+        <v>855.5301730393328</v>
       </c>
       <c r="E51">
-        <v>-406.5488790644609</v>
+        <v>-396.5538030043734</v>
       </c>
       <c r="F51">
-        <v>489.758726944286</v>
+        <v>499.7538030043735</v>
       </c>
       <c r="G51">
         <v>51.4</v>
@@ -5463,28 +5463,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M51">
-        <v>31.39353439712874</v>
+        <v>32.03421877258035</v>
       </c>
       <c r="N51">
-        <v>68.16646560287126</v>
+        <v>67.52578122741964</v>
       </c>
       <c r="O51">
-        <v>11.58829915248811</v>
+        <v>11.47938280866134</v>
       </c>
       <c r="P51">
-        <v>56.57816645038314</v>
+        <v>56.0463984187583</v>
       </c>
       <c r="Q51">
-        <v>96.27816645038314</v>
+        <v>95.7463984187583</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09187319358973556</v>
+        <v>0.09270750690225832</v>
       </c>
       <c r="T51">
-        <v>1.064046041333385</v>
+        <v>1.083314247165319</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.171353653289379</v>
+        <v>3.107926580223591</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07295525345112916</v>
+        <v>0.07298570817149319</v>
       </c>
       <c r="C52">
-        <v>407.1763700349593</v>
+        <v>396.8612627792351</v>
       </c>
       <c r="D52">
-        <v>855.5301730393328</v>
+        <v>855.2101418436961</v>
       </c>
       <c r="E52">
-        <v>-396.5538030043734</v>
+        <v>-386.558726944286</v>
       </c>
       <c r="F52">
-        <v>499.7538030043735</v>
+        <v>509.7488790644609</v>
       </c>
       <c r="G52">
         <v>51.4</v>
@@ -5545,28 +5545,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M52">
-        <v>32.03421877258035</v>
+        <v>32.67490314803195</v>
       </c>
       <c r="N52">
-        <v>67.52578122741964</v>
+        <v>66.88509685196803</v>
       </c>
       <c r="O52">
-        <v>11.47938280866134</v>
+        <v>11.37046646483457</v>
       </c>
       <c r="P52">
-        <v>56.0463984187583</v>
+        <v>55.51463038713347</v>
       </c>
       <c r="Q52">
-        <v>95.7463984187583</v>
+        <v>95.21463038713347</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09270750690225832</v>
+        <v>0.09357587381937385</v>
       </c>
       <c r="T52">
-        <v>1.083314247165319</v>
+        <v>1.103368910378149</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.107926580223591</v>
+        <v>3.046986843356462</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07298570817149319</v>
+        <v>0.0763826428918572</v>
       </c>
       <c r="C53">
-        <v>396.8612627792351</v>
+        <v>352.612320665035</v>
       </c>
       <c r="D53">
-        <v>855.2101418436961</v>
+        <v>820.9562757895834</v>
       </c>
       <c r="E53">
-        <v>-386.558726944286</v>
+        <v>-376.5636508841985</v>
       </c>
       <c r="F53">
-        <v>509.7488790644609</v>
+        <v>519.7439551245484</v>
       </c>
       <c r="G53">
         <v>51.4</v>
@@ -5627,45 +5627,45 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M53">
-        <v>32.67490314803195</v>
+        <v>37.36959037345503</v>
       </c>
       <c r="N53">
-        <v>66.88509685196803</v>
+        <v>62.19040962654496</v>
       </c>
       <c r="O53">
-        <v>11.37046646483457</v>
+        <v>10.57236963651264</v>
       </c>
       <c r="P53">
-        <v>55.51463038713347</v>
+        <v>51.61803999003232</v>
       </c>
       <c r="Q53">
-        <v>95.21463038713347</v>
+        <v>91.31803999003232</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09357587381937385</v>
+        <v>0.09448042269136918</v>
       </c>
       <c r="T53">
-        <v>1.103368910378149</v>
+        <v>1.12425918455818</v>
       </c>
       <c r="U53">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.17</v>
       </c>
       <c r="W53">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.046986843356462</v>
+        <v>2.66419832288879</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0763826428918572</v>
+        <v>0.07647783761222123</v>
       </c>
       <c r="C54">
-        <v>352.612320665035</v>
+        <v>341.6968051089526</v>
       </c>
       <c r="D54">
-        <v>820.9562757895834</v>
+        <v>820.0358362935885</v>
       </c>
       <c r="E54">
-        <v>-376.5636508841985</v>
+        <v>-366.568574824111</v>
       </c>
       <c r="F54">
-        <v>519.7439551245484</v>
+        <v>529.7390311846359</v>
       </c>
       <c r="G54">
         <v>51.4</v>
@@ -5709,28 +5709,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M54">
-        <v>37.36959037345503</v>
+        <v>38.08823634217532</v>
       </c>
       <c r="N54">
-        <v>62.19040962654496</v>
+        <v>61.47176365782467</v>
       </c>
       <c r="O54">
-        <v>10.57236963651264</v>
+        <v>10.45019982183019</v>
       </c>
       <c r="P54">
-        <v>51.61803999003232</v>
+        <v>51.02156383599447</v>
       </c>
       <c r="Q54">
-        <v>91.31803999003232</v>
+        <v>90.72156383599447</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09448042269136918</v>
+        <v>0.09542346300472601</v>
       </c>
       <c r="T54">
-        <v>1.12425918455818</v>
+        <v>1.146038406575659</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.66419832288879</v>
+        <v>2.613930430004096</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07647783761222123</v>
+        <v>0.07657303233258525</v>
       </c>
       <c r="C55">
-        <v>341.6968051089526</v>
+        <v>330.7833511975184</v>
       </c>
       <c r="D55">
-        <v>820.0358362935885</v>
+        <v>819.1174584422419</v>
       </c>
       <c r="E55">
-        <v>-366.568574824111</v>
+        <v>-356.5734987640235</v>
       </c>
       <c r="F55">
-        <v>529.7390311846359</v>
+        <v>539.7341072447234</v>
       </c>
       <c r="G55">
         <v>51.4</v>
@@ -5791,28 +5791,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M55">
-        <v>38.08823634217532</v>
+        <v>38.80688231089562</v>
       </c>
       <c r="N55">
-        <v>61.47176365782467</v>
+        <v>60.75311768910437</v>
       </c>
       <c r="O55">
-        <v>10.45019982183019</v>
+        <v>10.32803000714774</v>
       </c>
       <c r="P55">
-        <v>51.02156383599447</v>
+        <v>50.42508768195663</v>
       </c>
       <c r="Q55">
-        <v>90.72156383599447</v>
+        <v>90.12508768195663</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09542346300472601</v>
+        <v>0.09640750507083751</v>
       </c>
       <c r="T55">
-        <v>1.146038406575659</v>
+        <v>1.16876455128955</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.613930430004096</v>
+        <v>2.565524310929946</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07657303233258525</v>
+        <v>0.07666822705294929</v>
       </c>
       <c r="C56">
-        <v>330.7833511975184</v>
+        <v>319.8719520118249</v>
       </c>
       <c r="D56">
-        <v>819.1174584422419</v>
+        <v>818.2011353166357</v>
       </c>
       <c r="E56">
-        <v>-356.5734987640235</v>
+        <v>-346.5784227039361</v>
       </c>
       <c r="F56">
-        <v>539.7341072447234</v>
+        <v>549.7291833048108</v>
       </c>
       <c r="G56">
         <v>51.4</v>
@@ -5873,28 +5873,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M56">
-        <v>38.80688231089562</v>
+        <v>39.5255282796159</v>
       </c>
       <c r="N56">
-        <v>60.75311768910437</v>
+        <v>60.03447172038409</v>
       </c>
       <c r="O56">
-        <v>10.32803000714774</v>
+        <v>10.2058601924653</v>
       </c>
       <c r="P56">
-        <v>50.42508768195663</v>
+        <v>49.8286115279188</v>
       </c>
       <c r="Q56">
-        <v>90.12508768195663</v>
+        <v>89.5286115279188</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09640750507083751</v>
+        <v>0.0974352823398873</v>
       </c>
       <c r="T56">
-        <v>1.16876455128955</v>
+        <v>1.192500746879614</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.565524310929946</v>
+        <v>2.518878414367584</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07666822705294929</v>
+        <v>0.07857614177331329</v>
       </c>
       <c r="C57">
-        <v>319.8719520118249</v>
+        <v>291.9345385821978</v>
       </c>
       <c r="D57">
-        <v>818.2011353166357</v>
+        <v>800.2587979470961</v>
       </c>
       <c r="E57">
-        <v>-346.5784227039361</v>
+        <v>-336.5833466438486</v>
       </c>
       <c r="F57">
-        <v>549.7291833048108</v>
+        <v>559.7242593648983</v>
       </c>
       <c r="G57">
         <v>51.4</v>
@@ -5955,45 +5955,45 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M57">
-        <v>39.5255282796159</v>
+        <v>42.4270988598593</v>
       </c>
       <c r="N57">
-        <v>60.03447172038409</v>
+        <v>57.13290114014069</v>
       </c>
       <c r="O57">
-        <v>10.2058601924653</v>
+        <v>9.712593193823917</v>
       </c>
       <c r="P57">
-        <v>49.8286115279188</v>
+        <v>47.42030794631677</v>
       </c>
       <c r="Q57">
-        <v>89.5286115279188</v>
+        <v>87.12030794631677</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.0974352823398873</v>
+        <v>0.09850977675753023</v>
       </c>
       <c r="T57">
-        <v>1.192500746879614</v>
+        <v>1.217315860451044</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.17</v>
       </c>
       <c r="W57">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.518878414367584</v>
+        <v>2.34661343046</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07857614177331329</v>
+        <v>0.07870370649367732</v>
       </c>
       <c r="C58">
-        <v>291.9345385821978</v>
+        <v>280.7678480479233</v>
       </c>
       <c r="D58">
-        <v>800.2587979470961</v>
+        <v>799.0871834729091</v>
       </c>
       <c r="E58">
-        <v>-336.5833466438486</v>
+        <v>-326.5882705837611</v>
       </c>
       <c r="F58">
-        <v>559.7242593648983</v>
+        <v>569.7193354249858</v>
       </c>
       <c r="G58">
         <v>51.4</v>
@@ -6037,28 +6037,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M58">
-        <v>42.4270988598593</v>
+        <v>43.18472562521393</v>
       </c>
       <c r="N58">
-        <v>57.13290114014069</v>
+        <v>56.37527437478606</v>
       </c>
       <c r="O58">
-        <v>9.712593193823917</v>
+        <v>9.583796643713631</v>
       </c>
       <c r="P58">
-        <v>47.42030794631677</v>
+        <v>46.79147773107243</v>
       </c>
       <c r="Q58">
-        <v>87.12030794631677</v>
+        <v>86.49147773107242</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09850977675753023</v>
+        <v>0.09963424765971471</v>
       </c>
       <c r="T58">
-        <v>1.217315860451044</v>
+        <v>1.243285165351379</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.34661343046</v>
+        <v>2.305444773785263</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07870370649367732</v>
+        <v>0.07883127121404133</v>
       </c>
       <c r="C59">
-        <v>280.7678480479233</v>
+        <v>269.604583089856</v>
       </c>
       <c r="D59">
-        <v>799.0871834729091</v>
+        <v>797.9189945749293</v>
       </c>
       <c r="E59">
-        <v>-326.5882705837611</v>
+        <v>-316.5931945236736</v>
       </c>
       <c r="F59">
-        <v>569.7193354249858</v>
+        <v>579.7144114850734</v>
       </c>
       <c r="G59">
         <v>51.4</v>
@@ -6119,28 +6119,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M59">
-        <v>43.18472562521393</v>
+        <v>43.94235239056857</v>
       </c>
       <c r="N59">
-        <v>56.37527437478606</v>
+        <v>55.61764760943142</v>
       </c>
       <c r="O59">
-        <v>9.583796643713631</v>
+        <v>9.455000093603342</v>
       </c>
       <c r="P59">
-        <v>46.79147773107243</v>
+        <v>46.16264751582808</v>
       </c>
       <c r="Q59">
-        <v>86.49147773107242</v>
+        <v>85.86264751582809</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09963424765971471</v>
+        <v>0.1008122647953365</v>
       </c>
       <c r="T59">
-        <v>1.243285165351379</v>
+        <v>1.270491103818395</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.305444773785263</v>
+        <v>2.265695725961379</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07883127121404135</v>
+        <v>0.07895883593440536</v>
       </c>
       <c r="C60">
-        <v>269.604583089856</v>
+        <v>258.4447287063339</v>
       </c>
       <c r="D60">
-        <v>797.9189945749292</v>
+        <v>796.7542162514945</v>
       </c>
       <c r="E60">
-        <v>-316.5931945236737</v>
+        <v>-306.5981184635863</v>
       </c>
       <c r="F60">
-        <v>579.7144114850732</v>
+        <v>589.7094875451606</v>
       </c>
       <c r="G60">
         <v>51.4</v>
@@ -6201,28 +6201,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M60">
-        <v>43.94235239056856</v>
+        <v>44.69997915592318</v>
       </c>
       <c r="N60">
-        <v>55.61764760943143</v>
+        <v>54.86002084407681</v>
       </c>
       <c r="O60">
-        <v>9.455000093603344</v>
+        <v>9.326203543493058</v>
       </c>
       <c r="P60">
-        <v>46.16264751582808</v>
+        <v>45.53381730058375</v>
       </c>
       <c r="Q60">
-        <v>85.86264751582809</v>
+        <v>85.23381730058375</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1008122647953365</v>
+        <v>0.1020477461814765</v>
       </c>
       <c r="T60">
-        <v>1.270491103818395</v>
+        <v>1.299024161235023</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.265695725961379</v>
+        <v>2.227294103487458</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07895883593440536</v>
+        <v>0.07908640065476938</v>
       </c>
       <c r="C61">
-        <v>258.4447287063339</v>
+        <v>247.2882699831637</v>
       </c>
       <c r="D61">
-        <v>796.7542162514945</v>
+        <v>795.5928335884118</v>
       </c>
       <c r="E61">
-        <v>-306.5981184635863</v>
+        <v>-296.6030424034988</v>
       </c>
       <c r="F61">
-        <v>589.7094875451606</v>
+        <v>599.7045636052482</v>
       </c>
       <c r="G61">
         <v>51.4</v>
@@ -6283,28 +6283,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M61">
-        <v>44.69997915592318</v>
+        <v>45.45760592127781</v>
       </c>
       <c r="N61">
-        <v>54.86002084407681</v>
+        <v>54.10239407872218</v>
       </c>
       <c r="O61">
-        <v>9.326203543493058</v>
+        <v>9.197406993382771</v>
       </c>
       <c r="P61">
-        <v>45.53381730058375</v>
+        <v>44.90498708533941</v>
       </c>
       <c r="Q61">
-        <v>85.23381730058375</v>
+        <v>84.60498708533942</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1020477461814765</v>
+        <v>0.1033450016369235</v>
       </c>
       <c r="T61">
-        <v>1.299024161235023</v>
+        <v>1.328983871522482</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.227294103487458</v>
+        <v>2.190172535096001</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07908640065476938</v>
+        <v>0.07921396537513339</v>
       </c>
       <c r="C62">
-        <v>247.2882699831637</v>
+        <v>236.1351920929836</v>
       </c>
       <c r="D62">
-        <v>795.5928335884118</v>
+        <v>794.4348317583193</v>
       </c>
       <c r="E62">
-        <v>-296.6030424034988</v>
+        <v>-286.6079663434112</v>
       </c>
       <c r="F62">
-        <v>599.7045636052482</v>
+        <v>609.6996396653357</v>
       </c>
       <c r="G62">
         <v>51.4</v>
@@ -6365,28 +6365,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M62">
-        <v>45.45760592127781</v>
+        <v>46.21523268663245</v>
       </c>
       <c r="N62">
-        <v>54.10239407872218</v>
+        <v>53.34476731336754</v>
       </c>
       <c r="O62">
-        <v>9.197406993382771</v>
+        <v>9.068610443272483</v>
       </c>
       <c r="P62">
-        <v>44.90498708533941</v>
+        <v>44.27615687009506</v>
       </c>
       <c r="Q62">
-        <v>84.60498708533942</v>
+        <v>83.97615687009505</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1033450016369235</v>
+        <v>0.1047087830131626</v>
       </c>
       <c r="T62">
-        <v>1.328983871522482</v>
+        <v>1.360479977209297</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.190172535096001</v>
+        <v>2.154268067307541</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07921396537513339</v>
+        <v>0.07934153009549742</v>
       </c>
       <c r="C63">
-        <v>236.1351920929836</v>
+        <v>224.9854802946328</v>
       </c>
       <c r="D63">
-        <v>794.4348317583193</v>
+        <v>793.2801960200559</v>
       </c>
       <c r="E63">
-        <v>-286.6079663434112</v>
+        <v>-276.6128902833238</v>
       </c>
       <c r="F63">
-        <v>609.6996396653357</v>
+        <v>619.6947157254231</v>
       </c>
       <c r="G63">
         <v>51.4</v>
@@ -6447,28 +6447,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M63">
-        <v>46.21523268663245</v>
+        <v>46.97285945198707</v>
       </c>
       <c r="N63">
-        <v>53.34476731336754</v>
+        <v>52.58714054801292</v>
       </c>
       <c r="O63">
-        <v>9.068610443272483</v>
+        <v>8.939813893162198</v>
       </c>
       <c r="P63">
-        <v>44.27615687009506</v>
+        <v>43.64732665485072</v>
       </c>
       <c r="Q63">
-        <v>83.97615687009505</v>
+        <v>83.34732665485072</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1047087830131626</v>
+        <v>0.1061443423565722</v>
       </c>
       <c r="T63">
-        <v>1.360479977209297</v>
+        <v>1.393633772669103</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.154268067307541</v>
+        <v>2.11952180815742</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07934153009549742</v>
+        <v>0.07946909481586145</v>
       </c>
       <c r="C64">
-        <v>224.9854802946328</v>
+        <v>213.8391199325251</v>
       </c>
       <c r="D64">
-        <v>793.2801960200559</v>
+        <v>792.1289117180357</v>
       </c>
       <c r="E64">
-        <v>-276.6128902833238</v>
+        <v>-266.6178142232363</v>
       </c>
       <c r="F64">
-        <v>619.6947157254231</v>
+        <v>629.6897917855106</v>
       </c>
       <c r="G64">
         <v>51.4</v>
@@ -6529,28 +6529,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M64">
-        <v>46.97285945198707</v>
+        <v>47.73048621734171</v>
       </c>
       <c r="N64">
-        <v>52.58714054801292</v>
+        <v>51.82951378265828</v>
       </c>
       <c r="O64">
-        <v>8.939813893162198</v>
+        <v>8.811017343051908</v>
       </c>
       <c r="P64">
-        <v>43.64732665485072</v>
+        <v>43.01849643960637</v>
       </c>
       <c r="Q64">
-        <v>83.34732665485072</v>
+        <v>82.71849643960638</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1061443423565722</v>
+        <v>0.1076574995023282</v>
       </c>
       <c r="T64">
-        <v>1.393633772669103</v>
+        <v>1.428579665180791</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.11952180815742</v>
+        <v>2.085878604853334</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07946909481586145</v>
+        <v>0.07959665953622547</v>
       </c>
       <c r="C65">
-        <v>213.8391199325251</v>
+        <v>202.6960964360301</v>
       </c>
       <c r="D65">
-        <v>792.1289117180357</v>
+        <v>790.9809642816282</v>
       </c>
       <c r="E65">
-        <v>-266.6178142232363</v>
+        <v>-256.6227381631488</v>
       </c>
       <c r="F65">
-        <v>629.6897917855106</v>
+        <v>639.6848678455981</v>
       </c>
       <c r="G65">
         <v>51.4</v>
@@ -6611,28 +6611,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M65">
-        <v>47.73048621734171</v>
+        <v>48.48811298269634</v>
       </c>
       <c r="N65">
-        <v>51.82951378265828</v>
+        <v>51.07188701730365</v>
       </c>
       <c r="O65">
-        <v>8.811017343051908</v>
+        <v>8.682220792941621</v>
       </c>
       <c r="P65">
-        <v>43.01849643960637</v>
+        <v>42.38966622436203</v>
       </c>
       <c r="Q65">
-        <v>82.71849643960638</v>
+        <v>82.08966622436203</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1076574995023282</v>
+        <v>0.1092547209339596</v>
       </c>
       <c r="T65">
-        <v>1.428579665180791</v>
+        <v>1.46546699616535</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.085878604853334</v>
+        <v>2.0532867516525</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07959665953622547</v>
+        <v>0.07972422425658951</v>
       </c>
       <c r="C66">
-        <v>202.6960964360301</v>
+        <v>191.5563953188569</v>
       </c>
       <c r="D66">
-        <v>790.9809642816282</v>
+        <v>789.8363392245424</v>
       </c>
       <c r="E66">
-        <v>-256.6227381631488</v>
+        <v>-246.6276621030614</v>
       </c>
       <c r="F66">
-        <v>639.6848678455981</v>
+        <v>649.6799439056855</v>
       </c>
       <c r="G66">
         <v>51.4</v>
@@ -6693,28 +6693,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M66">
-        <v>48.48811298269634</v>
+        <v>49.24573974805097</v>
       </c>
       <c r="N66">
-        <v>51.07188701730365</v>
+        <v>50.31426025194902</v>
       </c>
       <c r="O66">
-        <v>8.682220792941621</v>
+        <v>8.553424242831335</v>
       </c>
       <c r="P66">
-        <v>42.38966622436203</v>
+        <v>41.76083600911769</v>
       </c>
       <c r="Q66">
-        <v>82.08966622436203</v>
+        <v>81.46083600911768</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1092547209339596</v>
+        <v>0.1109432121616843</v>
       </c>
       <c r="T66">
-        <v>1.46546699616535</v>
+        <v>1.504462174634741</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.0532867516525</v>
+        <v>2.021697724704</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07972422425658951</v>
+        <v>0.08763054897695351</v>
       </c>
       <c r="C67">
-        <v>191.5563953188569</v>
+        <v>116.5519946435011</v>
       </c>
       <c r="D67">
-        <v>789.8363392245424</v>
+        <v>724.8270146092741</v>
       </c>
       <c r="E67">
-        <v>-246.6276621030614</v>
+        <v>-236.6325860429739</v>
       </c>
       <c r="F67">
-        <v>649.6799439056855</v>
+        <v>659.675019965773</v>
       </c>
       <c r="G67">
         <v>51.4</v>
@@ -6775,45 +6775,45 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M67">
-        <v>49.24573974805097</v>
+        <v>59.37075179691957</v>
       </c>
       <c r="N67">
-        <v>50.31426025194902</v>
+        <v>40.18924820308042</v>
       </c>
       <c r="O67">
-        <v>8.553424242831335</v>
+        <v>6.832172194523672</v>
       </c>
       <c r="P67">
-        <v>41.76083600911769</v>
+        <v>33.35707600855675</v>
       </c>
       <c r="Q67">
-        <v>81.46083600911768</v>
+        <v>73.05707600855675</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1109432121616843</v>
+        <v>0.1127310264028045</v>
       </c>
       <c r="T67">
-        <v>1.504462174634741</v>
+        <v>1.545751187131743</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.17</v>
       </c>
       <c r="W67">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.021697724704</v>
+        <v>1.676919981416938</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08763054897695351</v>
+        <v>0.08787597369731753</v>
       </c>
       <c r="C68">
-        <v>116.5519946435011</v>
+        <v>104.7097421173073</v>
       </c>
       <c r="D68">
-        <v>724.8270146092741</v>
+        <v>722.9798381431679</v>
       </c>
       <c r="E68">
-        <v>-236.6325860429739</v>
+        <v>-226.6375099828864</v>
       </c>
       <c r="F68">
-        <v>659.675019965773</v>
+        <v>669.6700960258605</v>
       </c>
       <c r="G68">
         <v>51.4</v>
@@ -6857,28 +6857,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M68">
-        <v>59.37075179691957</v>
+        <v>60.27030864232744</v>
       </c>
       <c r="N68">
-        <v>40.18924820308042</v>
+        <v>39.28969135767255</v>
       </c>
       <c r="O68">
-        <v>6.832172194523672</v>
+        <v>6.679247530804333</v>
       </c>
       <c r="P68">
-        <v>33.35707600855675</v>
+        <v>32.61044382686821</v>
       </c>
       <c r="Q68">
-        <v>73.05707600855675</v>
+        <v>72.31044382686821</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1127310264028045</v>
+        <v>0.1146271930221744</v>
       </c>
       <c r="T68">
-        <v>1.545751187131743</v>
+        <v>1.589542564022503</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.676919981416938</v>
+        <v>1.651891324977879</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08787597369731753</v>
+        <v>0.08812139841768155</v>
       </c>
       <c r="C69">
-        <v>104.7097421173073</v>
+        <v>92.87688048716814</v>
       </c>
       <c r="D69">
-        <v>722.9798381431679</v>
+        <v>721.1420525731162</v>
       </c>
       <c r="E69">
-        <v>-226.6375099828864</v>
+        <v>-216.6424339227989</v>
       </c>
       <c r="F69">
-        <v>669.6700960258605</v>
+        <v>679.665172085948</v>
       </c>
       <c r="G69">
         <v>51.4</v>
@@ -6939,28 +6939,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M69">
-        <v>60.27030864232744</v>
+        <v>61.16986548773532</v>
       </c>
       <c r="N69">
-        <v>39.28969135767255</v>
+        <v>38.39013451226467</v>
       </c>
       <c r="O69">
-        <v>6.679247530804333</v>
+        <v>6.526322867084994</v>
       </c>
       <c r="P69">
-        <v>32.61044382686821</v>
+        <v>31.86381164517967</v>
       </c>
       <c r="Q69">
-        <v>72.31044382686821</v>
+        <v>71.56381164517967</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1146271930221744</v>
+        <v>0.1166418700552549</v>
       </c>
       <c r="T69">
-        <v>1.589542564022503</v>
+        <v>1.636070901968935</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.651891324977879</v>
+        <v>1.62759880549291</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08812139841768155</v>
+        <v>0.08836682313804559</v>
       </c>
       <c r="C70">
-        <v>92.87688048716814</v>
+        <v>81.05333832082499</v>
       </c>
       <c r="D70">
-        <v>721.1420525731162</v>
+        <v>719.3135864668604</v>
       </c>
       <c r="E70">
-        <v>-216.6424339227989</v>
+        <v>-206.6473578627115</v>
       </c>
       <c r="F70">
-        <v>679.665172085948</v>
+        <v>689.6602481460354</v>
       </c>
       <c r="G70">
         <v>51.4</v>
@@ -7021,28 +7021,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M70">
-        <v>61.16986548773532</v>
+        <v>62.06942233314319</v>
       </c>
       <c r="N70">
-        <v>38.39013451226467</v>
+        <v>37.4905776668568</v>
       </c>
       <c r="O70">
-        <v>6.526322867084994</v>
+        <v>6.373398203365657</v>
       </c>
       <c r="P70">
-        <v>31.86381164517967</v>
+        <v>31.11717946349114</v>
       </c>
       <c r="Q70">
-        <v>71.56381164517967</v>
+        <v>70.81717946349114</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1166418700552549</v>
+        <v>0.1187865262517599</v>
       </c>
       <c r="T70">
-        <v>1.636070901968935</v>
+        <v>1.685601068169976</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.62759880549291</v>
+        <v>1.604010417007506</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08836682313804559</v>
+        <v>0.0886122478584096</v>
       </c>
       <c r="C71">
-        <v>81.05333832082499</v>
+        <v>69.23904490865755</v>
       </c>
       <c r="D71">
-        <v>719.3135864668604</v>
+        <v>717.4943691147805</v>
       </c>
       <c r="E71">
-        <v>-206.6473578627115</v>
+        <v>-196.652281802624</v>
       </c>
       <c r="F71">
-        <v>689.6602481460354</v>
+        <v>699.6553242061229</v>
       </c>
       <c r="G71">
         <v>51.4</v>
@@ -7103,28 +7103,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M71">
-        <v>62.06942233314319</v>
+        <v>62.96897917855106</v>
       </c>
       <c r="N71">
-        <v>37.4905776668568</v>
+        <v>36.59102082144893</v>
       </c>
       <c r="O71">
-        <v>6.373398203365657</v>
+        <v>6.220473539646318</v>
       </c>
       <c r="P71">
-        <v>31.11717946349114</v>
+        <v>30.37054728180261</v>
       </c>
       <c r="Q71">
-        <v>70.81717946349114</v>
+        <v>70.07054728180262</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1187865262517599</v>
+        <v>0.121074159528032</v>
       </c>
       <c r="T71">
-        <v>1.685601068169976</v>
+        <v>1.738433245451086</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.604010417007506</v>
+        <v>1.581095982478827</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0886122478584096</v>
+        <v>0.08885767257877364</v>
       </c>
       <c r="C72">
-        <v>69.23904490865755</v>
+        <v>57.43393025456771</v>
       </c>
       <c r="D72">
-        <v>717.4943691147805</v>
+        <v>715.6843305207782</v>
       </c>
       <c r="E72">
-        <v>-196.652281802624</v>
+        <v>-186.6572057425365</v>
       </c>
       <c r="F72">
-        <v>699.6553242061229</v>
+        <v>709.6504002662105</v>
       </c>
       <c r="G72">
         <v>51.4</v>
@@ -7185,28 +7185,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M72">
-        <v>62.96897917855106</v>
+        <v>63.86853602395894</v>
       </c>
       <c r="N72">
-        <v>36.59102082144893</v>
+        <v>35.69146397604105</v>
       </c>
       <c r="O72">
-        <v>6.220473539646318</v>
+        <v>6.067548875926978</v>
       </c>
       <c r="P72">
-        <v>30.37054728180261</v>
+        <v>29.62391510011407</v>
       </c>
       <c r="Q72">
-        <v>70.07054728180262</v>
+        <v>69.32391510011408</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.121074159528032</v>
+        <v>0.1235195606164608</v>
       </c>
       <c r="T72">
-        <v>1.738433245451086</v>
+        <v>1.794909021165377</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.581095982478827</v>
+        <v>1.558827024979125</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08885767257877361</v>
+        <v>0.08910309729913765</v>
       </c>
       <c r="C73">
-        <v>57.43393025456805</v>
+        <v>45.63792506700372</v>
       </c>
       <c r="D73">
-        <v>715.6843305207784</v>
+        <v>713.8834013933015</v>
       </c>
       <c r="E73">
-        <v>-186.6572057425366</v>
+        <v>-176.6621296824492</v>
       </c>
       <c r="F73">
-        <v>709.6504002662103</v>
+        <v>719.6454763262977</v>
       </c>
       <c r="G73">
         <v>51.4</v>
@@ -7267,28 +7267,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M73">
-        <v>63.86853602395893</v>
+        <v>64.7680928693668</v>
       </c>
       <c r="N73">
-        <v>35.69146397604106</v>
+        <v>34.79190713063319</v>
       </c>
       <c r="O73">
-        <v>6.06754887592698</v>
+        <v>5.914624212207643</v>
       </c>
       <c r="P73">
-        <v>29.62391510011408</v>
+        <v>28.87728291842555</v>
       </c>
       <c r="Q73">
-        <v>69.32391510011408</v>
+        <v>68.57728291842555</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1235195606164608</v>
+        <v>0.1261396332112059</v>
       </c>
       <c r="T73">
-        <v>1.794909021165376</v>
+        <v>1.855418780859258</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.558827024979125</v>
+        <v>1.537176649632193</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08910309729913765</v>
+        <v>0.08934852201950166</v>
       </c>
       <c r="C74">
-        <v>45.63792506700372</v>
+        <v>33.85096075011529</v>
       </c>
       <c r="D74">
-        <v>713.8834013933015</v>
+        <v>712.0915131365006</v>
       </c>
       <c r="E74">
-        <v>-176.6621296824492</v>
+        <v>-166.6670536223617</v>
       </c>
       <c r="F74">
-        <v>719.6454763262977</v>
+        <v>729.6405523863853</v>
       </c>
       <c r="G74">
         <v>51.4</v>
@@ -7349,28 +7349,28 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M74">
-        <v>64.7680928693668</v>
+        <v>65.66764971477467</v>
       </c>
       <c r="N74">
-        <v>34.79190713063319</v>
+        <v>33.89235028522532</v>
       </c>
       <c r="O74">
-        <v>5.914624212207643</v>
+        <v>5.761699548488305</v>
       </c>
       <c r="P74">
-        <v>28.87728291842555</v>
+        <v>28.13065073673701</v>
       </c>
       <c r="Q74">
-        <v>68.57728291842555</v>
+        <v>67.83065073673701</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1261396332112059</v>
+        <v>0.1289537852574136</v>
       </c>
       <c r="T74">
-        <v>1.855418780859258</v>
+        <v>1.92041074497491</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.537176649632193</v>
+        <v>1.51611943525367</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08934852201950166</v>
+        <v>0.126282240991388</v>
       </c>
       <c r="C75">
-        <v>33.85096075011529</v>
+        <v>-171.3793408363589</v>
       </c>
       <c r="D75">
-        <v>712.0915131365006</v>
+        <v>516.8562876101139</v>
       </c>
       <c r="E75">
-        <v>-166.6670536223617</v>
+        <v>-156.6719775622742</v>
       </c>
       <c r="F75">
-        <v>729.6405523863853</v>
+        <v>739.6356284464728</v>
       </c>
       <c r="G75">
         <v>51.4</v>
@@ -7431,45 +7431,45 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M75">
-        <v>65.66764971477467</v>
+        <v>108.5785102559422</v>
       </c>
       <c r="N75">
-        <v>33.89235028522532</v>
+        <v>-9.018510255942218</v>
       </c>
       <c r="O75">
-        <v>5.761699548488305</v>
+        <v>-1.533146743510177</v>
       </c>
       <c r="P75">
-        <v>28.13065073673701</v>
+        <v>-7.48536351243204</v>
       </c>
       <c r="Q75">
-        <v>67.83065073673701</v>
+        <v>32.21463648756797</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1289537852574136</v>
+        <v>0.1330145344759084</v>
       </c>
       <c r="T75">
-        <v>1.92041074497491</v>
+        <v>2.014192482122596</v>
       </c>
       <c r="U75">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.17</v>
+        <v>0.15587983257556</v>
       </c>
       <c r="W75">
-        <v>0.07469999999999999</v>
+        <v>0.1239168405779078</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.51611943525367</v>
+        <v>0.9169401916209413</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.126282240991388</v>
+        <v>0.127292240991388</v>
       </c>
       <c r="C76">
-        <v>-171.3793408363589</v>
+        <v>-185.2207464990037</v>
       </c>
       <c r="D76">
-        <v>516.8562876101139</v>
+        <v>513.0099580075566</v>
       </c>
       <c r="E76">
-        <v>-156.6719775622742</v>
+        <v>-146.6769015021866</v>
       </c>
       <c r="F76">
-        <v>739.6356284464728</v>
+        <v>749.6307045065603</v>
       </c>
       <c r="G76">
         <v>51.4</v>
@@ -7513,37 +7513,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M76">
-        <v>108.5785102559422</v>
+        <v>110.0457874215631</v>
       </c>
       <c r="N76">
-        <v>-9.018510255942218</v>
+        <v>-10.48578742156307</v>
       </c>
       <c r="O76">
-        <v>-1.533146743510177</v>
+        <v>-1.782583861665723</v>
       </c>
       <c r="P76">
-        <v>-7.48536351243204</v>
+        <v>-8.703203559897352</v>
       </c>
       <c r="Q76">
-        <v>32.21463648756797</v>
+        <v>30.99679644010265</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1330145344759084</v>
+        <v>0.1365031158549447</v>
       </c>
       <c r="T76">
-        <v>2.014192482122596</v>
+        <v>2.0947601814075</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.15587983257556</v>
+        <v>0.1538014348078859</v>
       </c>
       <c r="W76">
-        <v>0.1239168405779078</v>
+        <v>0.1242219493702024</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9169401916209413</v>
+        <v>0.9047143223993286</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.127292240991388</v>
+        <v>0.128302240991388</v>
       </c>
       <c r="C77">
-        <v>-185.2207464990037</v>
+        <v>-199.0053279747802</v>
       </c>
       <c r="D77">
-        <v>513.0099580075566</v>
+        <v>509.2204525918674</v>
       </c>
       <c r="E77">
-        <v>-146.6769015021866</v>
+        <v>-136.6818254420992</v>
       </c>
       <c r="F77">
-        <v>749.6307045065603</v>
+        <v>759.6257805666477</v>
       </c>
       <c r="G77">
         <v>51.4</v>
@@ -7595,37 +7595,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M77">
-        <v>110.0457874215631</v>
+        <v>111.5130645871839</v>
       </c>
       <c r="N77">
-        <v>-10.48578742156307</v>
+        <v>-11.9530645871839</v>
       </c>
       <c r="O77">
-        <v>-1.782583861665723</v>
+        <v>-2.032020979821263</v>
       </c>
       <c r="P77">
-        <v>-8.703203559897352</v>
+        <v>-9.921043607362639</v>
       </c>
       <c r="Q77">
-        <v>30.99679644010265</v>
+        <v>29.77895639263736</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1365031158549447</v>
+        <v>0.1402824123489008</v>
       </c>
       <c r="T77">
-        <v>2.0947601814075</v>
+        <v>2.182041855632812</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1538014348078859</v>
+        <v>0.1517777317183084</v>
       </c>
       <c r="W77">
-        <v>0.1242219493702024</v>
+        <v>0.1245190289837523</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9047143223993286</v>
+        <v>0.8928101865782849</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.128302240991388</v>
+        <v>0.1293122409913879</v>
       </c>
       <c r="C78">
-        <v>-199.0053279747802</v>
+        <v>-212.7343352779355</v>
       </c>
       <c r="D78">
-        <v>509.2204525918674</v>
+        <v>505.4865213487997</v>
       </c>
       <c r="E78">
-        <v>-136.6818254420992</v>
+        <v>-126.6867493820117</v>
       </c>
       <c r="F78">
-        <v>759.6257805666477</v>
+        <v>769.6208566267352</v>
       </c>
       <c r="G78">
         <v>51.4</v>
@@ -7677,37 +7677,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M78">
-        <v>111.5130645871839</v>
+        <v>112.9803417528047</v>
       </c>
       <c r="N78">
-        <v>-11.9530645871839</v>
+        <v>-13.42034175280475</v>
       </c>
       <c r="O78">
-        <v>-2.032020979821263</v>
+        <v>-2.281458097976807</v>
       </c>
       <c r="P78">
-        <v>-9.921043607362639</v>
+        <v>-11.13888365482794</v>
       </c>
       <c r="Q78">
-        <v>29.77895639263736</v>
+        <v>28.56111634517206</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1402824123489008</v>
+        <v>0.1443903433205921</v>
       </c>
       <c r="T78">
-        <v>2.182041855632812</v>
+        <v>2.276913240660325</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1517777317183084</v>
+        <v>0.1498065923453434</v>
       </c>
       <c r="W78">
-        <v>0.1245190289837523</v>
+        <v>0.1248083922437036</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8928101865782849</v>
+        <v>0.8812152490902553</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1293122409913879</v>
+        <v>0.1303222409913879</v>
       </c>
       <c r="C79">
-        <v>-212.7343352779355</v>
+        <v>-226.408982025972</v>
       </c>
       <c r="D79">
-        <v>505.4865213487997</v>
+        <v>501.8069506608507</v>
       </c>
       <c r="E79">
-        <v>-126.6867493820117</v>
+        <v>-116.6916733219242</v>
       </c>
       <c r="F79">
-        <v>769.6208566267352</v>
+        <v>779.6159326868227</v>
       </c>
       <c r="G79">
         <v>51.4</v>
@@ -7759,37 +7759,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M79">
-        <v>112.9803417528047</v>
+        <v>114.4476189184256</v>
       </c>
       <c r="N79">
-        <v>-13.42034175280475</v>
+        <v>-14.8876189184256</v>
       </c>
       <c r="O79">
-        <v>-2.281458097976807</v>
+        <v>-2.530895216132353</v>
       </c>
       <c r="P79">
-        <v>-11.13888365482794</v>
+        <v>-12.35672370229325</v>
       </c>
       <c r="Q79">
-        <v>28.56111634517206</v>
+        <v>27.34327629770675</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1443903433205921</v>
+        <v>0.1488717225624372</v>
       </c>
       <c r="T79">
-        <v>2.276913240660325</v>
+        <v>2.380409297053977</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1498065923453434</v>
+        <v>0.1478859950075826</v>
       </c>
       <c r="W79">
-        <v>0.1248083922437036</v>
+        <v>0.1250903359328869</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8812152490902553</v>
+        <v>0.8699176176916621</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1303222409913879</v>
+        <v>0.131332240991388</v>
       </c>
       <c r="C80">
-        <v>-226.408982025972</v>
+        <v>-240.0304467547836</v>
       </c>
       <c r="D80">
-        <v>501.8069506608507</v>
+        <v>498.1805619921265</v>
       </c>
       <c r="E80">
-        <v>-116.6916733219242</v>
+        <v>-106.6965972618368</v>
       </c>
       <c r="F80">
-        <v>779.6159326868227</v>
+        <v>789.6110087469101</v>
       </c>
       <c r="G80">
         <v>51.4</v>
@@ -7841,37 +7841,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M80">
-        <v>114.4476189184256</v>
+        <v>115.9148960840464</v>
       </c>
       <c r="N80">
-        <v>-14.8876189184256</v>
+        <v>-16.35489608404643</v>
       </c>
       <c r="O80">
-        <v>-2.530895216132353</v>
+        <v>-2.780332334287893</v>
       </c>
       <c r="P80">
-        <v>-12.35672370229325</v>
+        <v>-13.57456374975854</v>
       </c>
       <c r="Q80">
-        <v>27.34327629770675</v>
+        <v>26.12543625024146</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1488717225624372</v>
+        <v>0.1537798998273152</v>
       </c>
       <c r="T80">
-        <v>2.380409297053977</v>
+        <v>2.493762120723214</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1478859950075826</v>
+        <v>0.1460140203872334</v>
       </c>
       <c r="W80">
-        <v>0.1250903359328869</v>
+        <v>0.1253651418071541</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8699176176916621</v>
+        <v>0.8589060022778436</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.131332240991388</v>
+        <v>0.132342240991388</v>
       </c>
       <c r="C81">
-        <v>-240.0304467547836</v>
+        <v>-253.5998741771759</v>
       </c>
       <c r="D81">
-        <v>498.1805619921265</v>
+        <v>494.6062106298216</v>
       </c>
       <c r="E81">
-        <v>-106.6965972618368</v>
+        <v>-96.7015212017493</v>
       </c>
       <c r="F81">
-        <v>789.6110087469101</v>
+        <v>799.6060848069976</v>
       </c>
       <c r="G81">
         <v>51.4</v>
@@ -7923,37 +7923,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M81">
-        <v>115.9148960840464</v>
+        <v>117.3821732496673</v>
       </c>
       <c r="N81">
-        <v>-16.35489608404643</v>
+        <v>-17.82217324966727</v>
       </c>
       <c r="O81">
-        <v>-2.780332334287893</v>
+        <v>-3.029769452443436</v>
       </c>
       <c r="P81">
-        <v>-13.57456374975854</v>
+        <v>-14.79240379722384</v>
       </c>
       <c r="Q81">
-        <v>26.12543625024146</v>
+        <v>24.90759620277617</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1537798998273152</v>
+        <v>0.1591788948186809</v>
       </c>
       <c r="T81">
-        <v>2.493762120723214</v>
+        <v>2.618450226759375</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1460140203872334</v>
+        <v>0.144188845132393</v>
       </c>
       <c r="W81">
-        <v>0.1253651418071541</v>
+        <v>0.1256330775345647</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8589060022778436</v>
+        <v>0.8481696772493706</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.132342240991388</v>
+        <v>0.133352240991388</v>
       </c>
       <c r="C82">
-        <v>-253.5998741771759</v>
+        <v>-267.1183763875927</v>
       </c>
       <c r="D82">
-        <v>494.6062106298216</v>
+        <v>491.0827844794925</v>
       </c>
       <c r="E82">
-        <v>-96.7015212017493</v>
+        <v>-86.70644514166179</v>
       </c>
       <c r="F82">
-        <v>799.6060848069976</v>
+        <v>809.6011608670851</v>
       </c>
       <c r="G82">
         <v>51.4</v>
@@ -8005,37 +8005,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M82">
-        <v>117.3821732496673</v>
+        <v>118.8494504152881</v>
       </c>
       <c r="N82">
-        <v>-17.82217324966727</v>
+        <v>-19.28945041528812</v>
       </c>
       <c r="O82">
-        <v>-3.029769452443436</v>
+        <v>-3.27920657059898</v>
       </c>
       <c r="P82">
-        <v>-14.79240379722384</v>
+        <v>-16.01024384468914</v>
       </c>
       <c r="Q82">
-        <v>24.90759620277617</v>
+        <v>23.68975615531087</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1591788948186809</v>
+        <v>0.1651462050722957</v>
       </c>
       <c r="T82">
-        <v>2.618450226759375</v>
+        <v>2.756263396588816</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.144188845132393</v>
+        <v>0.1424087359332277</v>
       </c>
       <c r="W82">
-        <v>0.1256330775345647</v>
+        <v>0.1258943975650022</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8481696772493706</v>
+        <v>0.8376984466660451</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.133352240991388</v>
+        <v>0.134362240991388</v>
       </c>
       <c r="C83">
-        <v>-267.1183763875927</v>
+        <v>-280.5870340157149</v>
       </c>
       <c r="D83">
-        <v>491.0827844794925</v>
+        <v>487.6092029114575</v>
       </c>
       <c r="E83">
-        <v>-86.70644514166179</v>
+        <v>-76.71136908157439</v>
       </c>
       <c r="F83">
-        <v>809.6011608670851</v>
+        <v>819.5962369271725</v>
       </c>
       <c r="G83">
         <v>51.4</v>
@@ -8087,37 +8087,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M83">
-        <v>118.8494504152881</v>
+        <v>120.3167275809089</v>
       </c>
       <c r="N83">
-        <v>-19.28945041528812</v>
+        <v>-20.75672758090894</v>
       </c>
       <c r="O83">
-        <v>-3.27920657059898</v>
+        <v>-3.528643688754521</v>
       </c>
       <c r="P83">
-        <v>-16.01024384468914</v>
+        <v>-17.22808389215442</v>
       </c>
       <c r="Q83">
-        <v>23.68975615531087</v>
+        <v>22.47191610784558</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1651462050722957</v>
+        <v>0.1717765497985344</v>
       </c>
       <c r="T83">
-        <v>2.756263396588816</v>
+        <v>2.90938914084375</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1424087359332277</v>
+        <v>0.140672044031603</v>
       </c>
       <c r="W83">
-        <v>0.1258943975650022</v>
+        <v>0.1261493439361607</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8376984466660451</v>
+        <v>0.8274826119506056</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.134362240991388</v>
+        <v>0.1353722409913879</v>
       </c>
       <c r="C84">
-        <v>-280.5870340157149</v>
+        <v>-294.006897331447</v>
       </c>
       <c r="D84">
-        <v>487.6092029114575</v>
+        <v>484.184415655813</v>
       </c>
       <c r="E84">
-        <v>-76.71136908157439</v>
+        <v>-66.71629302148688</v>
       </c>
       <c r="F84">
-        <v>819.5962369271725</v>
+        <v>829.59131298726</v>
       </c>
       <c r="G84">
         <v>51.4</v>
@@ -8169,37 +8169,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M84">
-        <v>120.3167275809089</v>
+        <v>121.7840047465298</v>
       </c>
       <c r="N84">
-        <v>-20.75672758090894</v>
+        <v>-22.2240047465298</v>
       </c>
       <c r="O84">
-        <v>-3.528643688754521</v>
+        <v>-3.778080806910066</v>
       </c>
       <c r="P84">
-        <v>-17.22808389215442</v>
+        <v>-18.44592393961974</v>
       </c>
       <c r="Q84">
-        <v>22.47191610784558</v>
+        <v>21.25407606038027</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1717765497985344</v>
+        <v>0.1791869350808011</v>
       </c>
       <c r="T84">
-        <v>2.90938914084375</v>
+        <v>3.080529678540442</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.140672044031603</v>
+        <v>0.1389772001276077</v>
       </c>
       <c r="W84">
-        <v>0.1261493439361607</v>
+        <v>0.1263981470212672</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8274826119506056</v>
+        <v>0.8175129419271042</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1353722409913879</v>
+        <v>0.136382240991388</v>
       </c>
       <c r="C85">
-        <v>-294.006897331447</v>
+        <v>-307.3789873036578</v>
       </c>
       <c r="D85">
-        <v>484.184415655813</v>
+        <v>480.8074017436897</v>
       </c>
       <c r="E85">
-        <v>-66.71629302148688</v>
+        <v>-56.72121696139936</v>
       </c>
       <c r="F85">
-        <v>829.59131298726</v>
+        <v>839.5863890473476</v>
       </c>
       <c r="G85">
         <v>51.4</v>
@@ -8251,37 +8251,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M85">
-        <v>121.7840047465298</v>
+        <v>123.2512819121506</v>
       </c>
       <c r="N85">
-        <v>-22.2240047465298</v>
+        <v>-23.69128191215064</v>
       </c>
       <c r="O85">
-        <v>-3.778080806910066</v>
+        <v>-4.027517925065609</v>
       </c>
       <c r="P85">
-        <v>-18.44592393961974</v>
+        <v>-19.66376398708503</v>
       </c>
       <c r="Q85">
-        <v>21.25407606038027</v>
+        <v>20.03623601291497</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1791869350808011</v>
+        <v>0.1875236185233512</v>
       </c>
       <c r="T85">
-        <v>3.080529678540442</v>
+        <v>3.27306278344922</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1389772001276077</v>
+        <v>0.1373227096498981</v>
       </c>
       <c r="W85">
-        <v>0.1263981470212672</v>
+        <v>0.126641026223395</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8175129419271042</v>
+        <v>0.8077806449994005</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.136382240991388</v>
+        <v>0.1840873798227443</v>
       </c>
       <c r="C86">
-        <v>-307.3789873036577</v>
+        <v>-436.5176959783839</v>
       </c>
       <c r="D86">
-        <v>480.8074017436897</v>
+        <v>361.663769129051</v>
       </c>
       <c r="E86">
-        <v>-56.72121696139948</v>
+        <v>-46.72614090131196</v>
       </c>
       <c r="F86">
-        <v>839.5863890473474</v>
+        <v>849.581465107435</v>
       </c>
       <c r="G86">
         <v>51.4</v>
@@ -8333,45 +8333,45 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M86">
-        <v>123.2512819121506</v>
+        <v>170.595958193573</v>
       </c>
       <c r="N86">
-        <v>-23.69128191215063</v>
+        <v>-71.03595819357297</v>
       </c>
       <c r="O86">
-        <v>-4.027517925065607</v>
+        <v>-12.07611289290741</v>
       </c>
       <c r="P86">
-        <v>-19.66376398708502</v>
+        <v>-58.95984530066556</v>
       </c>
       <c r="Q86">
-        <v>20.03623601291498</v>
+        <v>-19.25984530066556</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1875236185233511</v>
+        <v>0.2022727853006171</v>
       </c>
       <c r="T86">
-        <v>3.273062783449218</v>
+        <v>3.613690191700163</v>
       </c>
       <c r="U86">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1373227096498981</v>
+        <v>0.09921219810375109</v>
       </c>
       <c r="W86">
-        <v>0.126641026223395</v>
+        <v>0.1808781906207668</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8077806449994006</v>
+        <v>0.5836011653161828</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1840873798227443</v>
+        <v>0.1856373798227443</v>
       </c>
       <c r="C87">
-        <v>-436.5176959783839</v>
+        <v>-449.4013799404616</v>
       </c>
       <c r="D87">
-        <v>361.663769129051</v>
+        <v>358.7751612270608</v>
       </c>
       <c r="E87">
-        <v>-46.72614090131196</v>
+        <v>-36.73106484122457</v>
       </c>
       <c r="F87">
-        <v>849.581465107435</v>
+        <v>859.5765411675224</v>
       </c>
       <c r="G87">
         <v>51.4</v>
@@ -8415,37 +8415,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M87">
-        <v>170.595958193573</v>
+        <v>172.6029694664385</v>
       </c>
       <c r="N87">
-        <v>-71.03595819357297</v>
+        <v>-73.04296946643849</v>
       </c>
       <c r="O87">
-        <v>-12.07611289290741</v>
+        <v>-12.41730480929454</v>
       </c>
       <c r="P87">
-        <v>-58.95984530066556</v>
+        <v>-60.62566465714395</v>
       </c>
       <c r="Q87">
-        <v>-19.25984530066556</v>
+        <v>-20.92566465714395</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2022727853006171</v>
+        <v>0.2134494128220897</v>
       </c>
       <c r="T87">
-        <v>3.613690191700163</v>
+        <v>3.871810919678746</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.09921219810375109</v>
+        <v>0.09805856789324237</v>
       </c>
       <c r="W87">
-        <v>0.1808781906207668</v>
+        <v>0.1811098395670369</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5836011653161828</v>
+        <v>0.5768151052543669</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1856373798227443</v>
+        <v>0.1871873798227444</v>
       </c>
       <c r="C88">
-        <v>-449.4013799404616</v>
+        <v>-462.2392869106056</v>
       </c>
       <c r="D88">
-        <v>358.7751612270608</v>
+        <v>355.9323303170043</v>
       </c>
       <c r="E88">
-        <v>-36.73106484122457</v>
+        <v>-26.73598878113705</v>
       </c>
       <c r="F88">
-        <v>859.5765411675224</v>
+        <v>869.5716172276099</v>
       </c>
       <c r="G88">
         <v>51.4</v>
@@ -8497,37 +8497,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M88">
-        <v>172.6029694664385</v>
+        <v>174.6099807393041</v>
       </c>
       <c r="N88">
-        <v>-73.04296946643849</v>
+        <v>-75.04998073930408</v>
       </c>
       <c r="O88">
-        <v>-12.41730480929454</v>
+        <v>-12.75849672568169</v>
       </c>
       <c r="P88">
-        <v>-60.62566465714395</v>
+        <v>-62.29148401362238</v>
       </c>
       <c r="Q88">
-        <v>-20.92566465714395</v>
+        <v>-22.59148401362238</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2134494128220897</v>
+        <v>0.226345521500712</v>
       </c>
       <c r="T88">
-        <v>3.871810919678746</v>
+        <v>4.169642528884804</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.09805856789324237</v>
+        <v>0.09693145791745798</v>
       </c>
       <c r="W88">
-        <v>0.1811098395670369</v>
+        <v>0.1813361632501745</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5768151052543669</v>
+        <v>0.5701850465732822</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1871873798227444</v>
+        <v>0.1887373798227443</v>
       </c>
       <c r="C89">
-        <v>-462.2392869106056</v>
+        <v>-475.0324965052928</v>
       </c>
       <c r="D89">
-        <v>355.9323303170043</v>
+        <v>353.1341967824046</v>
       </c>
       <c r="E89">
-        <v>-26.73598878113705</v>
+        <v>-16.74091272104954</v>
       </c>
       <c r="F89">
-        <v>869.5716172276099</v>
+        <v>879.5666932876974</v>
       </c>
       <c r="G89">
         <v>51.4</v>
@@ -8579,37 +8579,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M89">
-        <v>174.6099807393041</v>
+        <v>176.6169920121696</v>
       </c>
       <c r="N89">
-        <v>-75.04998073930408</v>
+        <v>-77.05699201216966</v>
       </c>
       <c r="O89">
-        <v>-12.75849672568169</v>
+        <v>-13.09968864206884</v>
       </c>
       <c r="P89">
-        <v>-62.29148401362238</v>
+        <v>-63.95730337010082</v>
       </c>
       <c r="Q89">
-        <v>-22.59148401362238</v>
+        <v>-24.25730337010081</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.226345521500712</v>
+        <v>0.2413909816257714</v>
       </c>
       <c r="T89">
-        <v>4.169642528884804</v>
+        <v>4.517112739625205</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.09693145791745798</v>
+        <v>0.09582996407748684</v>
       </c>
       <c r="W89">
-        <v>0.1813361632501745</v>
+        <v>0.1815573432132406</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5701850465732822</v>
+        <v>0.5637056710440402</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1887373798227443</v>
+        <v>0.1902873798227444</v>
       </c>
       <c r="C90">
-        <v>-475.0324965052928</v>
+        <v>-487.782054656535</v>
       </c>
       <c r="D90">
-        <v>353.1341967824046</v>
+        <v>350.3797146912498</v>
       </c>
       <c r="E90">
-        <v>-16.74091272104954</v>
+        <v>-6.745836660962141</v>
       </c>
       <c r="F90">
-        <v>879.5666932876974</v>
+        <v>889.5617693477848</v>
       </c>
       <c r="G90">
         <v>51.4</v>
@@ -8661,37 +8661,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M90">
-        <v>176.6169920121696</v>
+        <v>178.6240032850352</v>
       </c>
       <c r="N90">
-        <v>-77.05699201216966</v>
+        <v>-79.06400328503521</v>
       </c>
       <c r="O90">
-        <v>-13.09968864206884</v>
+        <v>-13.44088055845599</v>
       </c>
       <c r="P90">
-        <v>-63.95730337010082</v>
+        <v>-65.62312272657923</v>
       </c>
       <c r="Q90">
-        <v>-24.25730337010081</v>
+        <v>-25.92312272657922</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2413909816257714</v>
+        <v>0.2591719799553869</v>
       </c>
       <c r="T90">
-        <v>4.517112739625205</v>
+        <v>4.927759352318406</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.09582996407748684</v>
+        <v>0.09475322290807689</v>
       </c>
       <c r="W90">
-        <v>0.1815573432132406</v>
+        <v>0.1817735528400582</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5637056710440402</v>
+        <v>0.5573718994592758</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1902873798227444</v>
+        <v>0.1918373798227443</v>
       </c>
       <c r="C91">
-        <v>-487.782054656535</v>
+        <v>-500.4889749154199</v>
       </c>
       <c r="D91">
-        <v>350.3797146912498</v>
+        <v>347.6678704924524</v>
       </c>
       <c r="E91">
-        <v>-6.745836660962141</v>
+        <v>3.249239399125372</v>
       </c>
       <c r="F91">
-        <v>889.5617693477848</v>
+        <v>899.5568454078723</v>
       </c>
       <c r="G91">
         <v>51.4</v>
@@ -8743,37 +8743,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M91">
-        <v>178.6240032850352</v>
+        <v>180.6310145579008</v>
       </c>
       <c r="N91">
-        <v>-79.06400328503521</v>
+        <v>-81.07101455790077</v>
       </c>
       <c r="O91">
-        <v>-13.44088055845599</v>
+        <v>-13.78207247484313</v>
       </c>
       <c r="P91">
-        <v>-65.62312272657923</v>
+        <v>-67.28894208305763</v>
       </c>
       <c r="Q91">
-        <v>-25.92312272657922</v>
+        <v>-27.58894208305763</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2591719799553869</v>
+        <v>0.2805091779509256</v>
       </c>
       <c r="T91">
-        <v>4.927759352318406</v>
+        <v>5.420535287550246</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.09475322290807689</v>
+        <v>0.09370040932020939</v>
       </c>
       <c r="W91">
-        <v>0.1817735528400582</v>
+        <v>0.181984957808502</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5573718994592758</v>
+        <v>0.5511788783541727</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1918373798227443</v>
+        <v>0.1933873798227443</v>
       </c>
       <c r="C92">
-        <v>-500.4889749154199</v>
+        <v>-513.1542396955861</v>
       </c>
       <c r="D92">
-        <v>347.6678704924524</v>
+        <v>344.9976817723738</v>
       </c>
       <c r="E92">
-        <v>3.249239399125372</v>
+        <v>13.24431545921288</v>
       </c>
       <c r="F92">
-        <v>899.5568454078723</v>
+        <v>909.5519214679598</v>
       </c>
       <c r="G92">
         <v>51.4</v>
@@ -8825,37 +8825,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M92">
-        <v>180.6310145579008</v>
+        <v>182.6380258307663</v>
       </c>
       <c r="N92">
-        <v>-81.07101455790077</v>
+        <v>-83.07802583076635</v>
       </c>
       <c r="O92">
-        <v>-13.78207247484313</v>
+        <v>-14.12326439123028</v>
       </c>
       <c r="P92">
-        <v>-67.28894208305763</v>
+        <v>-68.95476143953607</v>
       </c>
       <c r="Q92">
-        <v>-27.58894208305763</v>
+        <v>-29.25476143953607</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2805091779509256</v>
+        <v>0.3065879755010285</v>
       </c>
       <c r="T92">
-        <v>5.420535287550246</v>
+        <v>6.022816986166941</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.09370040932020939</v>
+        <v>0.09267073449251474</v>
       </c>
       <c r="W92">
-        <v>0.181984957808502</v>
+        <v>0.182191716513903</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5511788783541727</v>
+        <v>0.5451219676030279</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1933873798227443</v>
+        <v>0.1949373798227443</v>
       </c>
       <c r="C93">
-        <v>-513.1542396955861</v>
+        <v>-525.7788014598318</v>
       </c>
       <c r="D93">
-        <v>344.9976817723738</v>
+        <v>342.3681960682155</v>
       </c>
       <c r="E93">
-        <v>13.24431545921288</v>
+        <v>23.23939151930028</v>
       </c>
       <c r="F93">
-        <v>909.5519214679598</v>
+        <v>919.5469975280472</v>
       </c>
       <c r="G93">
         <v>51.4</v>
@@ -8907,37 +8907,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M93">
-        <v>182.6380258307663</v>
+        <v>184.6450371036319</v>
       </c>
       <c r="N93">
-        <v>-83.07802583076635</v>
+        <v>-85.0850371036319</v>
       </c>
       <c r="O93">
-        <v>-14.12326439123028</v>
+        <v>-14.46445630761743</v>
       </c>
       <c r="P93">
-        <v>-68.95476143953607</v>
+        <v>-70.62058079601448</v>
       </c>
       <c r="Q93">
-        <v>-29.25476143953607</v>
+        <v>-30.92058079601448</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3065879755010285</v>
+        <v>0.3391864724386571</v>
       </c>
       <c r="T93">
-        <v>6.022816986166941</v>
+        <v>6.77566910943781</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.09267073449251474</v>
+        <v>0.09166344390020482</v>
       </c>
       <c r="W93">
-        <v>0.182191716513903</v>
+        <v>0.1823939804648389</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5451219676030279</v>
+        <v>0.5391967288247341</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1949373798227443</v>
+        <v>0.1964873798227443</v>
       </c>
       <c r="C94">
-        <v>-525.7788014598318</v>
+        <v>-538.3635838528703</v>
       </c>
       <c r="D94">
-        <v>342.3681960682155</v>
+        <v>339.7784897352644</v>
       </c>
       <c r="E94">
-        <v>23.23939151930028</v>
+        <v>33.2344675793878</v>
       </c>
       <c r="F94">
-        <v>919.5469975280472</v>
+        <v>929.5420735881347</v>
       </c>
       <c r="G94">
         <v>51.4</v>
@@ -8989,37 +8989,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M94">
-        <v>184.6450371036319</v>
+        <v>186.6520483764974</v>
       </c>
       <c r="N94">
-        <v>-85.0850371036319</v>
+        <v>-87.09204837649746</v>
       </c>
       <c r="O94">
-        <v>-14.46445630761743</v>
+        <v>-14.80564822400457</v>
       </c>
       <c r="P94">
-        <v>-70.62058079601448</v>
+        <v>-72.28640015249289</v>
       </c>
       <c r="Q94">
-        <v>-30.92058079601448</v>
+        <v>-32.58640015249289</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3391864724386571</v>
+        <v>0.3810988256441797</v>
       </c>
       <c r="T94">
-        <v>6.77566910943781</v>
+        <v>7.743621839357498</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09166344390020482</v>
+        <v>0.09067781547117036</v>
       </c>
       <c r="W94">
-        <v>0.1823939804648389</v>
+        <v>0.182591894653389</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5391967288247341</v>
+        <v>0.5333989145362963</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1964873798227443</v>
+        <v>0.1980373798227443</v>
       </c>
       <c r="C95">
-        <v>-538.3635838528703</v>
+        <v>-550.9094827830617</v>
       </c>
       <c r="D95">
-        <v>339.7784897352644</v>
+        <v>337.2276668651606</v>
       </c>
       <c r="E95">
-        <v>33.2344675793878</v>
+        <v>43.22954363947531</v>
       </c>
       <c r="F95">
-        <v>929.5420735881347</v>
+        <v>939.5371496482222</v>
       </c>
       <c r="G95">
         <v>51.4</v>
@@ -9071,37 +9071,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M95">
-        <v>186.6520483764974</v>
+        <v>188.659059649363</v>
       </c>
       <c r="N95">
-        <v>-87.09204837649746</v>
+        <v>-89.09905964936304</v>
       </c>
       <c r="O95">
-        <v>-14.80564822400457</v>
+        <v>-15.14684014039172</v>
       </c>
       <c r="P95">
-        <v>-72.28640015249289</v>
+        <v>-73.95221950897133</v>
       </c>
       <c r="Q95">
-        <v>-32.58640015249289</v>
+        <v>-34.25221950897132</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3810988256441797</v>
+        <v>0.436981963251543</v>
       </c>
       <c r="T95">
-        <v>7.743621839357498</v>
+        <v>9.034225479250416</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09067781547117036</v>
+        <v>0.08971315785977492</v>
       </c>
       <c r="W95">
-        <v>0.182591894653389</v>
+        <v>0.1827855979017572</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5333989145362963</v>
+        <v>0.527724457998676</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1980373798227443</v>
+        <v>0.1995873798227443</v>
       </c>
       <c r="C96">
-        <v>-550.9094827830617</v>
+        <v>-563.4173674557818</v>
       </c>
       <c r="D96">
-        <v>337.2276668651606</v>
+        <v>334.7148582525278</v>
       </c>
       <c r="E96">
-        <v>43.22954363947531</v>
+        <v>53.22461969956271</v>
       </c>
       <c r="F96">
-        <v>939.5371496482222</v>
+        <v>949.5322257083096</v>
       </c>
       <c r="G96">
         <v>51.4</v>
@@ -9153,37 +9153,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M96">
-        <v>188.659059649363</v>
+        <v>190.6660709222286</v>
       </c>
       <c r="N96">
-        <v>-89.09905964936304</v>
+        <v>-91.1060709222286</v>
       </c>
       <c r="O96">
-        <v>-15.14684014039172</v>
+        <v>-15.48803205677886</v>
       </c>
       <c r="P96">
-        <v>-73.95221950897133</v>
+        <v>-75.61803886544973</v>
       </c>
       <c r="Q96">
-        <v>-34.25221950897132</v>
+        <v>-35.91803886544973</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.436981963251543</v>
+        <v>0.5152183559018518</v>
       </c>
       <c r="T96">
-        <v>9.034225479250416</v>
+        <v>10.8410705751005</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.08971315785977492</v>
+        <v>0.08876880882967203</v>
       </c>
       <c r="W96">
-        <v>0.1827855979017572</v>
+        <v>0.1829752231870019</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.527724457998676</v>
+        <v>0.5221694637039531</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1995873798227443</v>
+        <v>0.2011373798227443</v>
       </c>
       <c r="C97">
-        <v>-563.4173674557818</v>
+        <v>-575.8880813609342</v>
       </c>
       <c r="D97">
-        <v>334.7148582525278</v>
+        <v>332.2392204074631</v>
       </c>
       <c r="E97">
-        <v>53.22461969956271</v>
+        <v>63.21969575965022</v>
       </c>
       <c r="F97">
-        <v>949.5322257083096</v>
+        <v>959.5273017683971</v>
       </c>
       <c r="G97">
         <v>51.4</v>
@@ -9235,37 +9235,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M97">
-        <v>190.6660709222286</v>
+        <v>192.6730821950941</v>
       </c>
       <c r="N97">
-        <v>-91.1060709222286</v>
+        <v>-93.11308219509415</v>
       </c>
       <c r="O97">
-        <v>-15.48803205677886</v>
+        <v>-15.82922397316601</v>
       </c>
       <c r="P97">
-        <v>-75.61803886544973</v>
+        <v>-77.28385822192814</v>
       </c>
       <c r="Q97">
-        <v>-35.91803886544973</v>
+        <v>-37.58385822192814</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5152183559018518</v>
+        <v>0.632572944877315</v>
       </c>
       <c r="T97">
-        <v>10.8410705751005</v>
+        <v>13.55133821887564</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.08876880882967203</v>
+        <v>0.08784413373769628</v>
       </c>
       <c r="W97">
-        <v>0.1829752231870019</v>
+        <v>0.1831608979454706</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5221694637039531</v>
+        <v>0.5167301984570369</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2011373798227443</v>
+        <v>0.2026873798227443</v>
       </c>
       <c r="C98">
-        <v>-575.8880813609339</v>
+        <v>-588.3224432169577</v>
       </c>
       <c r="D98">
-        <v>332.2392204074632</v>
+        <v>329.7999346115269</v>
       </c>
       <c r="E98">
-        <v>63.21969575965011</v>
+        <v>73.21477181973762</v>
       </c>
       <c r="F98">
-        <v>959.527301768397</v>
+        <v>969.5223778284845</v>
       </c>
       <c r="G98">
         <v>51.4</v>
@@ -9317,37 +9317,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M98">
-        <v>192.6730821950941</v>
+        <v>194.6800934679597</v>
       </c>
       <c r="N98">
-        <v>-93.11308219509415</v>
+        <v>-95.12009346795971</v>
       </c>
       <c r="O98">
-        <v>-15.82922397316601</v>
+        <v>-16.17041588955315</v>
       </c>
       <c r="P98">
-        <v>-77.28385822192814</v>
+        <v>-78.94967757840655</v>
       </c>
       <c r="Q98">
-        <v>-37.58385822192814</v>
+        <v>-39.24967757840655</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6325729448773135</v>
+        <v>0.8281639265030848</v>
       </c>
       <c r="T98">
-        <v>13.5513382188756</v>
+        <v>18.0684509585008</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.08784413373769628</v>
+        <v>0.08693852411153447</v>
       </c>
       <c r="W98">
-        <v>0.1831608979454706</v>
+        <v>0.1833427443584039</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5167301984570369</v>
+        <v>0.5114030830090264</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2026873798227443</v>
+        <v>0.2042373798227443</v>
       </c>
       <c r="C99">
-        <v>-588.3224432169577</v>
+        <v>-600.7212478735557</v>
       </c>
       <c r="D99">
-        <v>329.7999346115269</v>
+        <v>327.3962060150164</v>
       </c>
       <c r="E99">
-        <v>73.21477181973762</v>
+        <v>83.20984787982513</v>
       </c>
       <c r="F99">
-        <v>969.5223778284845</v>
+        <v>979.517453888572</v>
       </c>
       <c r="G99">
         <v>51.4</v>
@@ -9399,37 +9399,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M99">
-        <v>194.6800934679597</v>
+        <v>196.6871047408253</v>
       </c>
       <c r="N99">
-        <v>-95.12009346795971</v>
+        <v>-97.12710474082529</v>
       </c>
       <c r="O99">
-        <v>-16.17041588955315</v>
+        <v>-16.5116078059403</v>
       </c>
       <c r="P99">
-        <v>-78.94967757840655</v>
+        <v>-80.61549693488499</v>
       </c>
       <c r="Q99">
-        <v>-39.24967757840655</v>
+        <v>-40.91549693488498</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8281639265030848</v>
+        <v>1.219345889754627</v>
       </c>
       <c r="T99">
-        <v>18.0684509585008</v>
+        <v>27.1026764377512</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.08693852411153447</v>
+        <v>0.086051396314478</v>
       </c>
       <c r="W99">
-        <v>0.1833427443584039</v>
+        <v>0.1835208796200528</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5114030830090264</v>
+        <v>0.5061846842028117</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2042373798227443</v>
+        <v>0.2057873798227443</v>
       </c>
       <c r="C100">
-        <v>-600.7212478735557</v>
+        <v>-613.0852671752309</v>
       </c>
       <c r="D100">
-        <v>327.3962060150164</v>
+        <v>325.0272627734286</v>
       </c>
       <c r="E100">
-        <v>83.20984787982513</v>
+        <v>93.20492393991253</v>
       </c>
       <c r="F100">
-        <v>979.517453888572</v>
+        <v>989.5125299486594</v>
       </c>
       <c r="G100">
         <v>51.4</v>
@@ -9481,37 +9481,37 @@
         <v>99.55999999999999</v>
       </c>
       <c r="M100">
-        <v>196.6871047408253</v>
+        <v>198.6941160136908</v>
       </c>
       <c r="N100">
-        <v>-97.12710474082529</v>
+        <v>-99.13411601369084</v>
       </c>
       <c r="O100">
-        <v>-16.5116078059403</v>
+        <v>-16.85279972232744</v>
       </c>
       <c r="P100">
-        <v>-80.61549693488499</v>
+        <v>-82.2813162913634</v>
       </c>
       <c r="Q100">
-        <v>-40.91549693488498</v>
+        <v>-42.58131629136339</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.219345889754627</v>
+        <v>2.392891779509254</v>
       </c>
       <c r="T100">
-        <v>27.1026764377512</v>
+        <v>54.20535287550241</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.086051396314478</v>
+        <v>0.08518219029109944</v>
       </c>
       <c r="W100">
-        <v>0.1835208796200528</v>
+        <v>0.1836954161895472</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5061846842028117</v>
+        <v>0.5010717075947024</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2057873798227443</v>
-      </c>
-      <c r="C101">
-        <v>-613.0852671752309</v>
-      </c>
-      <c r="D101">
-        <v>325.0272627734286</v>
-      </c>
-      <c r="E101">
-        <v>93.20492393991253</v>
-      </c>
-      <c r="F101">
-        <v>989.5125299486594</v>
-      </c>
-      <c r="G101">
-        <v>51.4</v>
-      </c>
-      <c r="H101">
-        <v>103.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>139.26</v>
-      </c>
-      <c r="K101">
-        <v>39.7</v>
-      </c>
-      <c r="L101">
-        <v>99.55999999999999</v>
-      </c>
-      <c r="M101">
-        <v>198.6941160136908</v>
-      </c>
-      <c r="N101">
-        <v>-99.13411601369084</v>
-      </c>
-      <c r="O101">
-        <v>-16.85279972232744</v>
-      </c>
-      <c r="P101">
-        <v>-82.2813162913634</v>
-      </c>
-      <c r="Q101">
-        <v>-42.58131629136339</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.392891779509254</v>
-      </c>
-      <c r="T101">
-        <v>54.20535287550241</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.08518219029109944</v>
-      </c>
-      <c r="W101">
-        <v>0.1836954161895472</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5010717075947024</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
